--- a/data/kapitola_02.xlsx
+++ b/data/kapitola_02.xlsx
@@ -124,7 +124,7 @@
     <t>9 až &lt; 10</t>
   </si>
   <si>
-    <t>Dolní hranice patří do intervalu, horní už ne. Intervaly mají šířku 1 hodina.</t>
+    <t>Dolní mez patří do intervalu, horní už ne. Intervaly mají šířku 1 hodina.</t>
   </si>
   <si>
     <t>Tři z 36 účastníků spánek neuvedli. Prázdná buňka neznamená 0 hodin.</t>

--- a/data/kapitola_02.xlsx
+++ b/data/kapitola_02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R Projects\github\statistics-for-psychology\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3B78C2-BDC9-4873-8BE4-3EB60FCCD27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FB27E0-9D80-461F-A6A0-B6398ED30607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4184" yWindow="2771" windowWidth="25839" windowHeight="16071" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cetnosti" sheetId="1" r:id="rId1"/>
@@ -106,27 +106,6 @@
     <t>Interval (h)</t>
   </si>
   <si>
-    <t>4 až &lt; 5</t>
-  </si>
-  <si>
-    <t>5 až &lt; 6</t>
-  </si>
-  <si>
-    <t>6 až &lt; 7</t>
-  </si>
-  <si>
-    <t>7 až &lt; 8</t>
-  </si>
-  <si>
-    <t>8 až &lt; 9</t>
-  </si>
-  <si>
-    <t>9 až &lt; 10</t>
-  </si>
-  <si>
-    <t>Dolní mez patří do intervalu, horní už ne. Intervaly mají šířku 1 hodina.</t>
-  </si>
-  <si>
     <t>Tři z 36 účastníků spánek neuvedli. Prázdná buňka neznamená 0 hodin.</t>
   </si>
   <si>
@@ -296,6 +275,27 @@
   </si>
   <si>
     <t>P36</t>
+  </si>
+  <si>
+    <t>&gt; 4 až 5</t>
+  </si>
+  <si>
+    <t>&gt; 5 až 6</t>
+  </si>
+  <si>
+    <t>&gt; 6 až 7</t>
+  </si>
+  <si>
+    <t>&gt; 7 až 8</t>
+  </si>
+  <si>
+    <t>&gt; 8 až 9</t>
+  </si>
+  <si>
+    <t>&gt; 9 až 10</t>
+  </si>
+  <si>
+    <t>Dolní mez nepatří do intervalu, horní ano. Intervaly mají šířku 1 hodina.</t>
   </si>
 </sst>
 </file>
@@ -741,22 +741,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4 až &lt; 5</c:v>
+                  <c:v>&gt; 4 až 5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5 až &lt; 6</c:v>
+                  <c:v>&gt; 5 až 6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6 až &lt; 7</c:v>
+                  <c:v>&gt; 6 až 7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7 až &lt; 8</c:v>
+                  <c:v>&gt; 7 až 8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8 až &lt; 9</c:v>
+                  <c:v>&gt; 8 až 9</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9 až &lt; 10</c:v>
+                  <c:v>&gt; 9 až 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -768,22 +768,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2239,19 +2239,19 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="D5" s="6">
-        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;="&amp;A5,Data!$B$2:$B$37,"&lt;"&amp;B5)</f>
-        <v>2</v>
+        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A5,Data!$B$2:$B$37,"&lt;="&amp;B5)</f>
+        <v>3</v>
       </c>
       <c r="E5" s="7">
         <f t="shared" ref="E5:E10" si="0">D5/$C$2</f>
-        <v>6.0606060606060608E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="F5" s="8">
         <f t="shared" ref="F5:F10" si="1">E5</f>
-        <v>6.0606060606060608E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -2273,19 +2273,19 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;="&amp;A6,Data!$B$2:$B$37,"&lt;"&amp;B6)</f>
-        <v>4</v>
+        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A6,Data!$B$2:$B$37,"&lt;="&amp;B6)</f>
+        <v>5</v>
       </c>
       <c r="E6" s="7">
         <f t="shared" si="0"/>
-        <v>0.12121212121212122</v>
+        <v>0.15151515151515152</v>
       </c>
       <c r="F6" s="8">
         <f t="shared" si="1"/>
-        <v>0.12121212121212122</v>
+        <v>0.15151515151515152</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -2307,19 +2307,19 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="D7" s="6">
-        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;="&amp;A7,Data!$B$2:$B$37,"&lt;"&amp;B7)</f>
-        <v>7</v>
+        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A7,Data!$B$2:$B$37,"&lt;="&amp;B7)</f>
+        <v>8</v>
       </c>
       <c r="E7" s="7">
         <f t="shared" si="0"/>
-        <v>0.21212121212121213</v>
+        <v>0.24242424242424243</v>
       </c>
       <c r="F7" s="8">
         <f t="shared" si="1"/>
-        <v>0.21212121212121213</v>
+        <v>0.24242424242424243</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -2341,19 +2341,19 @@
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="D8" s="6">
-        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;="&amp;A8,Data!$B$2:$B$37,"&lt;"&amp;B8)</f>
-        <v>11</v>
+        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A8,Data!$B$2:$B$37,"&lt;="&amp;B8)</f>
+        <v>10</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.30303030303030304</v>
       </c>
       <c r="F8" s="8">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.30303030303030304</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -2375,19 +2375,19 @@
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="D9" s="6">
-        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;="&amp;A9,Data!$B$2:$B$37,"&lt;"&amp;B9)</f>
-        <v>6</v>
+        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A9,Data!$B$2:$B$37,"&lt;="&amp;B9)</f>
+        <v>5</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="0"/>
-        <v>0.18181818181818182</v>
+        <v>0.15151515151515152</v>
       </c>
       <c r="F9" s="8">
         <f t="shared" si="1"/>
-        <v>0.18181818181818182</v>
+        <v>0.15151515151515152</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -2409,19 +2409,19 @@
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="D10" s="6">
-        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;="&amp;A10,Data!$B$2:$B$37,"&lt;"&amp;B10)</f>
-        <v>3</v>
+        <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A10,Data!$B$2:$B$37,"&lt;="&amp;B10)</f>
+        <v>2</v>
       </c>
       <c r="E10" s="7">
         <f t="shared" si="0"/>
-        <v>9.0909090909090912E-2</v>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="F10" s="8">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="14" spans="1:17" ht="22.1" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="15" spans="1:17" ht="22.1" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="17" spans="1:17" ht="22.1" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2587,7 +2587,7 @@
     </row>
     <row r="18" spans="1:17" ht="22.1" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -3042,23 +3042,23 @@
   <sheetData>
     <row r="1" spans="1:17" ht="36" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -3073,7 +3073,7 @@
     </row>
     <row r="2" spans="1:17" ht="22.1" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B2" s="13">
         <v>6</v>
@@ -3082,7 +3082,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E2" s="14">
         <v>2</v>
@@ -3102,7 +3102,7 @@
     </row>
     <row r="3" spans="1:17" ht="22.1" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B3" s="13">
         <v>8</v>
@@ -3111,14 +3111,14 @@
         <v>9</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E3" s="14">
         <v>4</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="4" spans="1:17" ht="22.1" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B4" s="13">
         <v>7</v>
@@ -3142,14 +3142,14 @@
         <v>8</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E4" s="14">
         <v>3</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="12" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="5" spans="1:17" ht="22.1" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B5" s="13">
         <v>5</v>
@@ -3173,14 +3173,14 @@
         <v>6</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E5" s="14">
         <v>2</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="12" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -3195,21 +3195,21 @@
     </row>
     <row r="6" spans="1:17" ht="22.1" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="14">
         <v>7</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E6" s="14">
         <v>3</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="12" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -3224,7 +3224,7 @@
     </row>
     <row r="7" spans="1:17" ht="22.1" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B7" s="13">
         <v>7</v>
@@ -3233,14 +3233,14 @@
         <v>0</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E7" s="14">
         <v>1</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="12" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="8" spans="1:17" ht="22.1" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B8" s="13">
         <v>4.5</v>
@@ -3264,14 +3264,14 @@
         <v>2</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E8" s="14">
         <v>1</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="12" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="9" spans="1:17" ht="22.1" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B9" s="13">
         <v>6.3</v>
@@ -3295,14 +3295,14 @@
         <v>7</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E9" s="14">
         <v>3</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="12" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="10" spans="1:17" ht="22.1" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B10" s="13">
         <v>7.3</v>
@@ -3326,14 +3326,14 @@
         <v>9</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E10" s="14">
         <v>4</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="12" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="11" spans="1:17" ht="22.1" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B11" s="13">
         <v>8.1</v>
@@ -3357,14 +3357,14 @@
         <v>4</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E11" s="14">
         <v>2</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="12" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -3379,21 +3379,21 @@
     </row>
     <row r="12" spans="1:17" ht="22.1" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="14">
         <v>7</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E12" s="14">
         <v>3</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="12" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -3408,7 +3408,7 @@
     </row>
     <row r="13" spans="1:17" ht="22.1" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B13" s="13">
         <v>6</v>
@@ -3417,7 +3417,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E13" s="14">
         <v>2</v>
@@ -3437,7 +3437,7 @@
     </row>
     <row r="14" spans="1:17" ht="22.1" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B14" s="13">
         <v>7.1</v>
@@ -3446,7 +3446,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E14" s="14">
         <v>3</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="15" spans="1:17" ht="22.1" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B15" s="13">
         <v>7.9</v>
@@ -3475,7 +3475,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E15" s="14">
         <v>1</v>
@@ -3495,7 +3495,7 @@
     </row>
     <row r="16" spans="1:17" ht="22.1" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B16" s="13">
         <v>9.1999999999999993</v>
@@ -3504,7 +3504,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E16" s="14">
         <v>3</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="17" spans="1:17" ht="22.1" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B17" s="13">
         <v>5.5</v>
@@ -3533,7 +3533,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E17" s="14">
         <v>4</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="18" spans="1:17" ht="22.1" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B18" s="13">
         <v>6.8</v>
@@ -3562,7 +3562,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E18" s="14">
         <v>2</v>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="19" spans="1:17" ht="22.1" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B19" s="13">
         <v>7.5</v>
@@ -3591,7 +3591,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E19" s="14">
         <v>4</v>
@@ -3611,7 +3611,7 @@
     </row>
     <row r="20" spans="1:17" ht="22.1" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B20" s="13">
         <v>8.8000000000000007</v>
@@ -3620,7 +3620,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E20" s="14">
         <v>2</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="21" spans="1:17" ht="22.1" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B21" s="13">
         <v>4.8</v>
@@ -3649,7 +3649,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E21" s="14">
         <v>3</v>
@@ -3669,7 +3669,7 @@
     </row>
     <row r="22" spans="1:17" ht="22.1" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B22" s="13">
         <v>6.5</v>
@@ -3678,7 +3678,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E22" s="14">
         <v>1</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="23" spans="1:17" ht="22.1" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B23" s="13">
         <v>7.4</v>
@@ -3707,7 +3707,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E23" s="14">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="24" spans="1:17" ht="22.1" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B24" s="13">
         <v>8.3000000000000007</v>
@@ -3736,7 +3736,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E24" s="14">
         <v>4</v>
@@ -3756,14 +3756,14 @@
     </row>
     <row r="25" spans="1:17" ht="22.1" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="14">
         <v>6</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E25" s="14">
         <v>3</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="26" spans="1:17" ht="22.1" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B26" s="13">
         <v>6.2</v>
@@ -3792,7 +3792,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E26" s="14">
         <v>4</v>
@@ -3812,7 +3812,7 @@
     </row>
     <row r="27" spans="1:17" ht="22.1" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B27" s="13">
         <v>7.2</v>
@@ -3821,7 +3821,7 @@
         <v>12</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E27" s="14">
         <v>2</v>
@@ -3841,7 +3841,7 @@
     </row>
     <row r="28" spans="1:17" ht="22.1" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B28" s="13">
         <v>8</v>
@@ -3850,7 +3850,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E28" s="14">
         <v>3</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="29" spans="1:17" ht="22.1" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B29" s="13">
         <v>9.5</v>
@@ -3879,7 +3879,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E29" s="14">
         <v>2</v>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="30" spans="1:17" ht="22.1" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B30" s="13">
         <v>5.8</v>
@@ -3908,7 +3908,7 @@
         <v>4</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E30" s="14">
         <v>3</v>
@@ -3928,7 +3928,7 @@
     </row>
     <row r="31" spans="1:17" ht="22.1" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B31" s="13">
         <v>7</v>
@@ -3937,7 +3937,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E31" s="14">
         <v>4</v>
@@ -3957,7 +3957,7 @@
     </row>
     <row r="32" spans="1:17" ht="22.1" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B32" s="13">
         <v>7.7</v>
@@ -3966,7 +3966,7 @@
         <v>10</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E32" s="14">
         <v>3</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="33" spans="1:17" ht="22.1" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B33" s="13">
         <v>9</v>
@@ -3995,7 +3995,7 @@
         <v>5</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E33" s="14">
         <v>4</v>
@@ -4015,7 +4015,7 @@
     </row>
     <row r="34" spans="1:17" ht="22.1" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B34" s="13">
         <v>5.2</v>
@@ -4024,7 +4024,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E34" s="14">
         <v>2</v>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="35" spans="1:17" ht="22.1" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B35" s="13">
         <v>6.5</v>
@@ -4053,7 +4053,7 @@
         <v>11</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E35" s="14">
         <v>3</v>
@@ -4073,7 +4073,7 @@
     </row>
     <row r="36" spans="1:17" ht="22.1" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B36" s="13">
         <v>7.5</v>
@@ -4082,7 +4082,7 @@
         <v>6</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E36" s="14">
         <v>2</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="37" spans="1:17" ht="22.1" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B37" s="13">
         <v>8.5</v>
@@ -4111,7 +4111,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E37" s="14">
         <v>3</v>

--- a/data/kapitola_02.xlsx
+++ b/data/kapitola_02.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R Projects\github\statistics-for-psychology\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FB27E0-9D80-461F-A6A0-B6398ED30607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73AE155-EF1B-484F-92CF-6DF8C0697109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cetnosti" sheetId="1" r:id="rId1"/>
-    <sheet name="Histogram" sheetId="2" r:id="rId2"/>
-    <sheet name="Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Prehled" sheetId="1" r:id="rId1"/>
+    <sheet name="Cetnosti" sheetId="2" r:id="rId2"/>
+    <sheet name="Histogram" sheetId="3" r:id="rId3"/>
+    <sheet name="Data" sheetId="4" r:id="rId4"/>
+    <sheet name="Sest_osob" sheetId="5" r:id="rId5"/>
+    <sheet name="Strategie" sheetId="6" r:id="rId6"/>
+    <sheet name="Tvary" sheetId="7" r:id="rId7"/>
+    <sheet name="Podlaha_strop" sheetId="8" r:id="rId8"/>
+    <sheet name="Stonek" sheetId="9" r:id="rId9"/>
+    <sheet name="U01_odpocatost" sheetId="10" r:id="rId10"/>
+    <sheet name="U03_chybeni" sheetId="11" r:id="rId11"/>
+    <sheet name="U03_ruseni" sheetId="12" r:id="rId12"/>
+    <sheet name="U04_chyby" sheetId="13" r:id="rId13"/>
+    <sheet name="U05_spanek" sheetId="14" r:id="rId14"/>
+    <sheet name="U08_stonek" sheetId="15" r:id="rId15"/>
+    <sheet name="Podpora" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +48,157 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="179">
+  <si>
+    <t>Data ke kapitole 2</t>
+  </si>
+  <si>
+    <t>Začněte vstupy. Žluté buňky obsahují data; modré buňky na výpočtových listech vzorce.</t>
+  </si>
+  <si>
+    <t>Zadání a vysvětlení jsou v kapitole. Řešení otevírejte až po vlastním pokusu.</t>
+  </si>
+  <si>
+    <t>Slovní úlohy bez konkrétních pozorování nevyžadují vlastní datový list.</t>
+  </si>
+  <si>
+    <t>Hladké modelové křivky jsou modely, nikoli další soubory naměřených hodnot.</t>
+  </si>
+  <si>
+    <t>List</t>
+  </si>
+  <si>
+    <t>Oblast vstupů / tabulky</t>
+  </si>
+  <si>
+    <t>Příklad nebo cvičení</t>
+  </si>
+  <si>
+    <t>Sest_osob</t>
+  </si>
+  <si>
+    <t>A2:E7</t>
+  </si>
+  <si>
+    <t>Úvodní příklad, jmenovatel procent</t>
+  </si>
+  <si>
+    <t>Strategie</t>
+  </si>
+  <si>
+    <t>A2:B4</t>
+  </si>
+  <si>
+    <t>Výsečový a sloupcový graf</t>
+  </si>
+  <si>
+    <t>Tvary</t>
+  </si>
+  <si>
+    <t>A2:G10</t>
+  </si>
+  <si>
+    <t>Obrázek: šest tvarů rozdělení</t>
+  </si>
+  <si>
+    <t>Podlaha_strop</t>
+  </si>
+  <si>
+    <t>A2:C14</t>
+  </si>
+  <si>
+    <t>Obrázek: meze nástroje</t>
+  </si>
+  <si>
+    <t>Stonek</t>
+  </si>
+  <si>
+    <t>A2:A9</t>
+  </si>
+  <si>
+    <t>Výklad: stonek a list</t>
+  </si>
+  <si>
+    <t>U01_odpocatost</t>
+  </si>
+  <si>
+    <t>A2:A13</t>
+  </si>
+  <si>
+    <t>Cvičení 1 a 2</t>
+  </si>
+  <si>
+    <t>U03_chybeni</t>
+  </si>
+  <si>
+    <t>Cvičení 3a</t>
+  </si>
+  <si>
+    <t>U03_ruseni</t>
+  </si>
+  <si>
+    <t>A2:C4</t>
+  </si>
+  <si>
+    <t>Cvičení 3b</t>
+  </si>
+  <si>
+    <t>U04_chyby</t>
+  </si>
+  <si>
+    <t>A2:A11</t>
+  </si>
+  <si>
+    <t>Cvičení 4</t>
+  </si>
+  <si>
+    <t>U05_spanek</t>
+  </si>
+  <si>
+    <t>Cvičení 5</t>
+  </si>
+  <si>
+    <t>U08_stonek</t>
+  </si>
+  <si>
+    <t>Cvičení 8: zadání k rekonstrukci</t>
+  </si>
+  <si>
+    <t>Podpora</t>
+  </si>
+  <si>
+    <t>A2:C3</t>
+  </si>
+  <si>
+    <t>Zavádějící graf; cvičení 9</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>A2:E37</t>
+  </si>
+  <si>
+    <t>36 osob; výklad a cvičení 10</t>
+  </si>
+  <si>
+    <t>Cetnosti</t>
+  </si>
+  <si>
+    <t>A4:H8</t>
+  </si>
+  <si>
+    <t>Hotové výpočty a graf odpočatosti</t>
+  </si>
+  <si>
+    <t>Histogram</t>
+  </si>
+  <si>
+    <t>A4:E10</t>
+  </si>
+  <si>
+    <t>Hotové intervalové četnosti a histogram</t>
+  </si>
   <si>
     <t>Odpočatost před úlohou</t>
   </si>
@@ -106,6 +269,27 @@
     <t>Interval (h)</t>
   </si>
   <si>
+    <t>&gt; 4 až 5</t>
+  </si>
+  <si>
+    <t>&gt; 5 až 6</t>
+  </si>
+  <si>
+    <t>&gt; 6 až 7</t>
+  </si>
+  <si>
+    <t>&gt; 7 až 8</t>
+  </si>
+  <si>
+    <t>&gt; 8 až 9</t>
+  </si>
+  <si>
+    <t>&gt; 9 až 10</t>
+  </si>
+  <si>
+    <t>Dolní mez nepatří do intervalu, horní ano. Intervaly mají šířku 1 hodina.</t>
+  </si>
+  <si>
     <t>Tři z 36 účastníků spánek neuvedli. Prázdná buňka neznamená 0 hodin.</t>
   </si>
   <si>
@@ -277,25 +461,130 @@
     <t>P36</t>
   </si>
   <si>
-    <t>&gt; 4 až 5</t>
-  </si>
-  <si>
-    <t>&gt; 5 až 6</t>
-  </si>
-  <si>
-    <t>&gt; 6 až 7</t>
-  </si>
-  <si>
-    <t>&gt; 7 až 8</t>
-  </si>
-  <si>
-    <t>&gt; 8 až 9</t>
-  </si>
-  <si>
-    <t>&gt; 9 až 10</t>
-  </si>
-  <si>
-    <t>Dolní mez nepatří do intervalu, horní ano. Intervaly mají šířku 1 hodina.</t>
+    <t>Použití a původ</t>
+  </si>
+  <si>
+    <t>Autorské ilustrační údaje. Nejde o skutečný výzkum.</t>
+  </si>
+  <si>
+    <t>Procvičování</t>
+  </si>
+  <si>
+    <t>Čtení</t>
+  </si>
+  <si>
+    <t>Vysvětlování</t>
+  </si>
+  <si>
+    <t>Hodnota</t>
+  </si>
+  <si>
+    <t>Souměrnost</t>
+  </si>
+  <si>
+    <t>Šikmost doprava</t>
+  </si>
+  <si>
+    <t>Šikmost doleva</t>
+  </si>
+  <si>
+    <t>Dva vrcholy</t>
+  </si>
+  <si>
+    <t>Rovnoměrnost</t>
+  </si>
+  <si>
+    <t>Odlehlost</t>
+  </si>
+  <si>
+    <t>Autorské schematické četnosti. Sloupce představují šest různých rozdělení, nikoli spárovaná měření lidí.</t>
+  </si>
+  <si>
+    <t>Počet správných odpovědí</t>
+  </si>
+  <si>
+    <t>Podlaha: četnost</t>
+  </si>
+  <si>
+    <t>Strop: četnost</t>
+  </si>
+  <si>
+    <t>Doba (s)</t>
+  </si>
+  <si>
+    <t>Odpočatost (kód 1–4)</t>
+  </si>
+  <si>
+    <t>Autorské údaje. 1 vůbec, 2 trochu, 3 dost, 4 zcela.</t>
+  </si>
+  <si>
+    <t>Odpověď</t>
+  </si>
+  <si>
+    <t>Ano</t>
+  </si>
+  <si>
+    <t>Ne</t>
+  </si>
+  <si>
+    <t>Chybí</t>
+  </si>
+  <si>
+    <t>Zadáno 25 oslovených; 20 odpovědělo. Četnosti, nikoli jednotliví lidé.</t>
+  </si>
+  <si>
+    <t>Možnost</t>
+  </si>
+  <si>
+    <t>Počet označení</t>
+  </si>
+  <si>
+    <t>Počet odpovídajících</t>
+  </si>
+  <si>
+    <t>Hluk</t>
+  </si>
+  <si>
+    <t>Telefon</t>
+  </si>
+  <si>
+    <t>Únava</t>
+  </si>
+  <si>
+    <t>Bylo možné označit více možností. Překryvy mezi lidmi nejsou zadány.</t>
+  </si>
+  <si>
+    <t>Počet chyb</t>
+  </si>
+  <si>
+    <t>Spánek (h)</t>
+  </si>
+  <si>
+    <t>Intervaly: více než 4 až 5 včetně, více než 5 až 6 včetně, více než 6 až 7 včetně, více než 7 až 8 včetně.</t>
+  </si>
+  <si>
+    <t>Listy</t>
+  </si>
+  <si>
+    <t>1 3 3 8</t>
+  </si>
+  <si>
+    <t>0 5</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Klíč: 2 | 3 znamená 23 sekund. Sloupec Listy je záměrně textový zápis zadání, nikoli hotové řešení.</t>
+  </si>
+  <si>
+    <t>Skupina</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -307,7 +596,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -343,10 +632,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF526775"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF223744"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,6 +668,11 @@
         <fgColor rgb="FFFFF8E7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF1CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -380,15 +685,21 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -426,6 +737,21 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -458,7 +784,7 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
-              <a:rPr lang="cs-CZ" sz="1125">
+              <a:rPr sz="1125">
                 <a:latin typeface="Arial"/>
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
@@ -488,7 +814,7 @@
               <a:srgbClr val="267888"/>
             </a:solidFill>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Cetnosti!$B$5:$B$8</c:f>
@@ -531,17 +857,8 @@
             </c:numRef>
           </c:val>
           <c:extLst>
-            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
-              <c14:invertSolidFillFmt>
-                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </c14:spPr>
-              </c14:invertSolidFillFmt>
-            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5B12-4AE9-AE0A-8CE683D2AECB}"/>
+              <c16:uniqueId val="{00000000-D822-41B8-9D4B-67F4E0AE0A1D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -581,7 +898,6 @@
               <a:lstStyle/>
               <a:p>
                 <a:r>
-                  <a:rPr lang="cs-CZ"/>
                   <a:t>Odpočatost</a:t>
                 </a:r>
               </a:p>
@@ -639,7 +955,6 @@
               <a:lstStyle/>
               <a:p>
                 <a:r>
-                  <a:rPr lang="cs-CZ"/>
                   <a:t>Počet účastníků</a:t>
                 </a:r>
               </a:p>
@@ -734,7 +1049,7 @@
               <a:srgbClr val="267888"/>
             </a:solidFill>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Histogram!$C$5:$C$10</c:f>
@@ -789,17 +1104,8 @@
             </c:numRef>
           </c:val>
           <c:extLst>
-            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
-              <c14:invertSolidFillFmt>
-                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </c14:spPr>
-              </c14:invertSolidFillFmt>
-            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9326-4A8A-AD6D-972A1E0DBE4A}"/>
+              <c16:uniqueId val="{00000000-5417-431E-B3D1-D106FC7FDDBC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -966,7 +1272,7 @@
         <xdr:cNvPr id="2" name="Chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1007,7 +1313,7 @@
         <xdr:cNvPr id="2" name="Chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1223,6 +1529,807 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+    </row>
+    <row r="4" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A4" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+    </row>
+    <row r="5" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A5" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+    </row>
+    <row r="6" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A6" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+    </row>
+    <row r="7" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="17">
+        <v>2</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="17">
+        <v>3</v>
+      </c>
+      <c r="C3" s="21"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="17">
+        <v>2</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="17">
+        <v>1</v>
+      </c>
+      <c r="C5" s="21"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="17">
+        <v>4</v>
+      </c>
+      <c r="C6" s="21"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1">
+      <c r="A7" s="17">
+        <v>3</v>
+      </c>
+      <c r="C7" s="21"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1">
+      <c r="A8" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1">
+      <c r="A9" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1">
+      <c r="A10" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1">
+      <c r="A11" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1">
+      <c r="A12" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1">
+      <c r="A13" s="17">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1">
+      <c r="A2" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="17">
+        <v>9</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1">
+      <c r="A3" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="17">
+        <v>11</v>
+      </c>
+      <c r="D3" s="21"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="17">
+        <v>5</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="D5" s="21"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="D7" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="3" width="22" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1">
+      <c r="A2" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="17">
+        <v>12</v>
+      </c>
+      <c r="C2" s="17">
+        <v>20</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1">
+      <c r="A3" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="17">
+        <v>14</v>
+      </c>
+      <c r="C3" s="17">
+        <v>20</v>
+      </c>
+      <c r="E3" s="21"/>
+    </row>
+    <row r="4" spans="1:5" ht="25" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="17">
+        <v>6</v>
+      </c>
+      <c r="C4" s="17">
+        <v>20</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="E5" s="21"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="E6" s="21"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="E7" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="17">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="17">
+        <v>1</v>
+      </c>
+      <c r="C3" s="21"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="17">
+        <v>1</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="17">
+        <v>2</v>
+      </c>
+      <c r="C5" s="21"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="17">
+        <v>2</v>
+      </c>
+      <c r="C6" s="21"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1">
+      <c r="A7" s="17">
+        <v>2</v>
+      </c>
+      <c r="C7" s="21"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1">
+      <c r="A8" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1">
+      <c r="A9" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1">
+      <c r="A10" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1">
+      <c r="A11" s="17">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="17">
+        <v>5</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="17">
+        <v>5.5</v>
+      </c>
+      <c r="C3" s="21"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="17">
+        <v>6</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="17">
+        <v>6</v>
+      </c>
+      <c r="C5" s="21"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="C6" s="21"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1">
+      <c r="A7" s="17">
+        <v>7</v>
+      </c>
+      <c r="C7" s="21"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1">
+      <c r="A8" s="17">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1">
+      <c r="A2" s="17">
+        <v>2</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1">
+      <c r="A3" s="17">
+        <v>3</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="21"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1">
+      <c r="A4" s="17">
+        <v>4</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="D5" s="21"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="D7" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="3" width="22" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1">
+      <c r="A2" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="17">
+        <v>30</v>
+      </c>
+      <c r="C2" s="17">
+        <v>40</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1">
+      <c r="A3" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="17">
+        <v>32</v>
+      </c>
+      <c r="C3" s="17">
+        <v>80</v>
+      </c>
+      <c r="E3" s="21"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="E4" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="E5" s="21"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="E6" s="21"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="E7" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q40"/>
   <sheetFormatPr defaultRowHeight="13.6"/>
   <cols>
@@ -1233,7 +2340,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="22.1" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1255,7 +2362,7 @@
     <row r="2" spans="1:17" ht="22.1" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1">
         <f>COUNT(Data!E2:E37)</f>
@@ -1296,29 +2403,29 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" ht="36" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>9</v>
+      <c r="A4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -1335,29 +2442,29 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="6">
+        <v>60</v>
+      </c>
+      <c r="C5" s="8">
         <f>COUNTIFS(Data!$E$2:$E$37,A5)</f>
         <v>4</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <f>C5/$C$2</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="10">
         <f>D5</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="8">
         <f>SUM($C$5:C5)</f>
         <v>4</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <f>F5/$C$2</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="10">
         <f>G5</f>
         <v>0.1111111111111111</v>
       </c>
@@ -1376,29 +2483,29 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="6">
+        <v>61</v>
+      </c>
+      <c r="C6" s="8">
         <f>COUNTIFS(Data!$E$2:$E$37,A6)</f>
         <v>10</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <f>C6/$C$2</f>
         <v>0.27777777777777779</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="10">
         <f>D6</f>
         <v>0.27777777777777779</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="8">
         <f>SUM($C$5:C6)</f>
         <v>14</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="9">
         <f>F6/$C$2</f>
         <v>0.3888888888888889</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="10">
         <f>G6</f>
         <v>0.3888888888888889</v>
       </c>
@@ -1417,29 +2524,29 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="6">
+        <v>62</v>
+      </c>
+      <c r="C7" s="8">
         <f>COUNTIFS(Data!$E$2:$E$37,A7)</f>
         <v>14</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="9">
         <f>C7/$C$2</f>
         <v>0.3888888888888889</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="10">
         <f>D7</f>
         <v>0.3888888888888889</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="8">
         <f>SUM($C$5:C7)</f>
         <v>28</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="9">
         <f>F7/$C$2</f>
         <v>0.77777777777777779</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="10">
         <f>G7</f>
         <v>0.77777777777777779</v>
       </c>
@@ -1458,29 +2565,29 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="6">
+        <v>63</v>
+      </c>
+      <c r="C8" s="8">
         <f>COUNTIFS(Data!$E$2:$E$37,A8)</f>
         <v>8</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="9">
         <f>C8/$C$2</f>
         <v>0.22222222222222221</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="10">
         <f>D8</f>
         <v>0.22222222222222221</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="8">
         <f>SUM($C$5:C8)</f>
         <v>36</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="9">
         <f>F8/$C$2</f>
         <v>1</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="10">
         <f>G8</f>
         <v>1</v>
       </c>
@@ -1498,8 +2605,8 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -1515,18 +2622,18 @@
     </row>
     <row r="10" spans="1:17" ht="22.1" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="9">
+      <c r="B10" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="11">
         <f>SUM(C5:C8)</f>
         <v>36</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="12">
         <f>SUM(D5:D8)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="13">
         <f>D10</f>
         <v>1</v>
       </c>
@@ -1563,8 +2670,8 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A12" s="12" t="s">
-        <v>15</v>
+      <c r="A12" s="14" t="s">
+        <v>65</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1584,8 +2691,8 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A13" s="12" t="s">
-        <v>16</v>
+      <c r="A13" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1624,8 +2731,8 @@
       <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A15" s="12" t="s">
-        <v>17</v>
+      <c r="A15" s="14" t="s">
+        <v>67</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2125,8 +3232,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q40"/>
   <sheetFormatPr defaultRowHeight="13.6"/>
   <cols>
@@ -2138,7 +3245,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="22.1" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2160,7 +3267,7 @@
     <row r="2" spans="1:17" ht="22.1" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1">
         <f>COUNT(Data!B2:B37)</f>
@@ -2201,23 +3308,23 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" ht="36" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>6</v>
+      <c r="A4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -2239,17 +3346,17 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="6">
+        <v>73</v>
+      </c>
+      <c r="D5" s="8">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A5,Data!$B$2:$B$37,"&lt;="&amp;B5)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <f t="shared" ref="E5:E10" si="0">D5/$C$2</f>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="10">
         <f t="shared" ref="F5:F10" si="1">E5</f>
         <v>9.0909090909090912E-2</v>
       </c>
@@ -2273,17 +3380,17 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="6">
+        <v>74</v>
+      </c>
+      <c r="D6" s="8">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A6,Data!$B$2:$B$37,"&lt;="&amp;B6)</f>
         <v>5</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <f t="shared" si="0"/>
         <v>0.15151515151515152</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="10">
         <f t="shared" si="1"/>
         <v>0.15151515151515152</v>
       </c>
@@ -2307,17 +3414,17 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="6">
+        <v>75</v>
+      </c>
+      <c r="D7" s="8">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A7,Data!$B$2:$B$37,"&lt;="&amp;B7)</f>
         <v>8</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <f t="shared" si="0"/>
         <v>0.24242424242424243</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="10">
         <f t="shared" si="1"/>
         <v>0.24242424242424243</v>
       </c>
@@ -2341,17 +3448,17 @@
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="6">
+        <v>76</v>
+      </c>
+      <c r="D8" s="8">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A8,Data!$B$2:$B$37,"&lt;="&amp;B8)</f>
         <v>10</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="9">
         <f t="shared" si="0"/>
         <v>0.30303030303030304</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="10">
         <f t="shared" si="1"/>
         <v>0.30303030303030304</v>
       </c>
@@ -2375,17 +3482,17 @@
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="6">
+        <v>77</v>
+      </c>
+      <c r="D9" s="8">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A9,Data!$B$2:$B$37,"&lt;="&amp;B9)</f>
         <v>5</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="9">
         <f t="shared" si="0"/>
         <v>0.15151515151515152</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="10">
         <f t="shared" si="1"/>
         <v>0.15151515151515152</v>
       </c>
@@ -2409,17 +3516,17 @@
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="6">
+        <v>78</v>
+      </c>
+      <c r="D10" s="8">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A10,Data!$B$2:$B$37,"&lt;="&amp;B10)</f>
         <v>2</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="9">
         <f t="shared" si="0"/>
         <v>6.0606060606060608E-2</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="10">
         <f t="shared" si="1"/>
         <v>6.0606060606060608E-2</v>
       </c>
@@ -2440,8 +3547,8 @@
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2457,18 +3564,18 @@
     <row r="12" spans="1:17" ht="22.1" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="9">
+      <c r="C12" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="11">
         <f>SUM(D5:D10)</f>
         <v>33</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="12">
         <f>SUM(E5:E10)</f>
         <v>1</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="13">
         <f>E12</f>
         <v>1</v>
       </c>
@@ -2504,8 +3611,8 @@
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A14" s="12" t="s">
-        <v>86</v>
+      <c r="A14" s="14" t="s">
+        <v>79</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -2525,8 +3632,8 @@
       <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A15" s="12" t="s">
-        <v>23</v>
+      <c r="A15" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2565,8 +3672,8 @@
       <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A17" s="12" t="s">
-        <v>24</v>
+      <c r="A17" s="14" t="s">
+        <v>81</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2586,8 +3693,8 @@
       <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A18" s="12" t="s">
-        <v>25</v>
+      <c r="A18" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -3030,8 +4137,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q40"/>
   <sheetFormatPr defaultRowHeight="13.6"/>
   <cols>
@@ -3041,24 +4148,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="36" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>30</v>
+      <c r="A1" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -3073,18 +4180,18 @@
     </row>
     <row r="2" spans="1:17" ht="22.1" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="13">
+        <v>89</v>
+      </c>
+      <c r="B2" s="15">
         <v>6</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="16">
         <v>5</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="14">
+      <c r="D2" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="16">
         <v>2</v>
       </c>
       <c r="F2" s="1"/>
@@ -3102,23 +4209,23 @@
     </row>
     <row r="3" spans="1:17" ht="22.1" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="13">
+        <v>91</v>
+      </c>
+      <c r="B3" s="15">
         <v>8</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="16">
         <v>9</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="14">
+      <c r="D3" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="16">
         <v>4</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="12" t="s">
-        <v>36</v>
+      <c r="G3" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -3133,23 +4240,23 @@
     </row>
     <row r="4" spans="1:17" ht="22.1" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="13">
+        <v>94</v>
+      </c>
+      <c r="B4" s="15">
         <v>7</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="16">
         <v>8</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="14">
+      <c r="D4" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="16">
         <v>3</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="12" t="s">
-        <v>38</v>
+      <c r="G4" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -3164,23 +4271,23 @@
     </row>
     <row r="5" spans="1:17" ht="22.1" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="13">
+        <v>96</v>
+      </c>
+      <c r="B5" s="15">
         <v>5</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="16">
         <v>6</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="14">
+      <c r="D5" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="16">
         <v>2</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="12" t="s">
-        <v>40</v>
+      <c r="G5" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -3195,21 +4302,21 @@
     </row>
     <row r="6" spans="1:17" ht="22.1" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="14">
+        <v>98</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="16">
         <v>7</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="14">
+      <c r="D6" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="16">
         <v>3</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="12" t="s">
-        <v>42</v>
+      <c r="G6" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -3224,23 +4331,23 @@
     </row>
     <row r="7" spans="1:17" ht="22.1" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="13">
+        <v>100</v>
+      </c>
+      <c r="B7" s="15">
         <v>7</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="16">
         <v>0</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="14">
+      <c r="D7" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="16">
         <v>1</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="12" t="s">
-        <v>44</v>
+      <c r="G7" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -3255,23 +4362,23 @@
     </row>
     <row r="8" spans="1:17" ht="22.1" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="13">
+        <v>102</v>
+      </c>
+      <c r="B8" s="15">
         <v>4.5</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="16">
         <v>2</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="14">
+      <c r="D8" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="16">
         <v>1</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="12" t="s">
-        <v>46</v>
+      <c r="G8" s="14" t="s">
+        <v>103</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -3286,23 +4393,23 @@
     </row>
     <row r="9" spans="1:17" ht="22.1" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="13">
+        <v>104</v>
+      </c>
+      <c r="B9" s="15">
         <v>6.3</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="16">
         <v>7</v>
       </c>
-      <c r="D9" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="14">
+      <c r="D9" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="16">
         <v>3</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="12" t="s">
-        <v>48</v>
+      <c r="G9" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -3317,23 +4424,23 @@
     </row>
     <row r="10" spans="1:17" ht="22.1" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="13">
+        <v>106</v>
+      </c>
+      <c r="B10" s="15">
         <v>7.3</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="16">
         <v>9</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="14">
+      <c r="D10" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="16">
         <v>4</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="12" t="s">
-        <v>50</v>
+      <c r="G10" s="14" t="s">
+        <v>107</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -3348,23 +4455,23 @@
     </row>
     <row r="11" spans="1:17" ht="22.1" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="13">
+        <v>108</v>
+      </c>
+      <c r="B11" s="15">
         <v>8.1</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="16">
         <v>4</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="14">
+      <c r="D11" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="16">
         <v>2</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="12" t="s">
-        <v>52</v>
+      <c r="G11" s="14" t="s">
+        <v>109</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -3379,21 +4486,21 @@
     </row>
     <row r="12" spans="1:17" ht="22.1" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14">
+        <v>110</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16">
         <v>7</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="14">
+      <c r="D12" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="16">
         <v>3</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="12" t="s">
-        <v>54</v>
+      <c r="G12" s="14" t="s">
+        <v>111</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -3408,18 +4515,18 @@
     </row>
     <row r="13" spans="1:17" ht="22.1" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="13">
+        <v>112</v>
+      </c>
+      <c r="B13" s="15">
         <v>6</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="16">
         <v>10</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="14">
+      <c r="D13" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="16">
         <v>2</v>
       </c>
       <c r="F13" s="1"/>
@@ -3437,18 +4544,18 @@
     </row>
     <row r="14" spans="1:17" ht="22.1" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="13">
+        <v>113</v>
+      </c>
+      <c r="B14" s="15">
         <v>7.1</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="16">
         <v>5</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="14">
+      <c r="D14" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="16">
         <v>3</v>
       </c>
       <c r="F14" s="1"/>
@@ -3466,18 +4573,18 @@
     </row>
     <row r="15" spans="1:17" ht="22.1" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="13">
+        <v>114</v>
+      </c>
+      <c r="B15" s="15">
         <v>7.9</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="16">
         <v>8</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="14">
+      <c r="D15" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="16">
         <v>1</v>
       </c>
       <c r="F15" s="1"/>
@@ -3495,18 +4602,18 @@
     </row>
     <row r="16" spans="1:17" ht="22.1" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="13">
+        <v>115</v>
+      </c>
+      <c r="B16" s="15">
         <v>9.1999999999999993</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="16">
         <v>11</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="14">
+      <c r="D16" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="16">
         <v>3</v>
       </c>
       <c r="F16" s="1"/>
@@ -3524,18 +4631,18 @@
     </row>
     <row r="17" spans="1:17" ht="22.1" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="13">
+        <v>116</v>
+      </c>
+      <c r="B17" s="15">
         <v>5.5</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="16">
         <v>6</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="14">
+      <c r="D17" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="16">
         <v>4</v>
       </c>
       <c r="F17" s="1"/>
@@ -3553,18 +4660,18 @@
     </row>
     <row r="18" spans="1:17" ht="22.1" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="13">
+        <v>117</v>
+      </c>
+      <c r="B18" s="15">
         <v>6.8</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="16">
         <v>8</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="14">
+      <c r="D18" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="16">
         <v>2</v>
       </c>
       <c r="F18" s="1"/>
@@ -3582,18 +4689,18 @@
     </row>
     <row r="19" spans="1:17" ht="22.1" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="13">
+        <v>118</v>
+      </c>
+      <c r="B19" s="15">
         <v>7.5</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="16">
         <v>3</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="14">
+      <c r="D19" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="16">
         <v>4</v>
       </c>
       <c r="F19" s="1"/>
@@ -3611,18 +4718,18 @@
     </row>
     <row r="20" spans="1:17" ht="22.1" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="13">
+        <v>119</v>
+      </c>
+      <c r="B20" s="15">
         <v>8.8000000000000007</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="16">
         <v>7</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="14">
+      <c r="D20" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="16">
         <v>2</v>
       </c>
       <c r="F20" s="1"/>
@@ -3640,18 +4747,18 @@
     </row>
     <row r="21" spans="1:17" ht="22.1" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="13">
+        <v>120</v>
+      </c>
+      <c r="B21" s="15">
         <v>4.8</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="16">
         <v>9</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="14">
+      <c r="D21" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="16">
         <v>3</v>
       </c>
       <c r="F21" s="1"/>
@@ -3669,18 +4776,18 @@
     </row>
     <row r="22" spans="1:17" ht="22.1" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="13">
+        <v>121</v>
+      </c>
+      <c r="B22" s="15">
         <v>6.5</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="16">
         <v>5</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="14">
+      <c r="D22" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="16">
         <v>1</v>
       </c>
       <c r="F22" s="1"/>
@@ -3698,18 +4805,18 @@
     </row>
     <row r="23" spans="1:17" ht="22.1" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="13">
+        <v>122</v>
+      </c>
+      <c r="B23" s="15">
         <v>7.4</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="16">
         <v>7</v>
       </c>
-      <c r="D23" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="14">
+      <c r="D23" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="16">
         <v>3</v>
       </c>
       <c r="F23" s="1"/>
@@ -3727,18 +4834,18 @@
     </row>
     <row r="24" spans="1:17" ht="22.1" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="13">
+        <v>123</v>
+      </c>
+      <c r="B24" s="15">
         <v>8.3000000000000007</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="16">
         <v>10</v>
       </c>
-      <c r="D24" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="14">
+      <c r="D24" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="16">
         <v>4</v>
       </c>
       <c r="F24" s="1"/>
@@ -3756,16 +4863,16 @@
     </row>
     <row r="25" spans="1:17" ht="22.1" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14">
+        <v>124</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="16">
         <v>6</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="14">
+      <c r="D25" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="16">
         <v>3</v>
       </c>
       <c r="F25" s="1"/>
@@ -3783,18 +4890,18 @@
     </row>
     <row r="26" spans="1:17" ht="22.1" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B26" s="13">
+        <v>125</v>
+      </c>
+      <c r="B26" s="15">
         <v>6.2</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="16">
         <v>8</v>
       </c>
-      <c r="D26" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="14">
+      <c r="D26" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="16">
         <v>4</v>
       </c>
       <c r="F26" s="1"/>
@@ -3812,18 +4919,18 @@
     </row>
     <row r="27" spans="1:17" ht="22.1" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" s="13">
+        <v>126</v>
+      </c>
+      <c r="B27" s="15">
         <v>7.2</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="16">
         <v>12</v>
       </c>
-      <c r="D27" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27" s="14">
+      <c r="D27" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="16">
         <v>2</v>
       </c>
       <c r="F27" s="1"/>
@@ -3841,18 +4948,18 @@
     </row>
     <row r="28" spans="1:17" ht="22.1" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="13">
+        <v>127</v>
+      </c>
+      <c r="B28" s="15">
         <v>8</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="16">
         <v>6</v>
       </c>
-      <c r="D28" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="14">
+      <c r="D28" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="16">
         <v>3</v>
       </c>
       <c r="F28" s="1"/>
@@ -3870,18 +4977,18 @@
     </row>
     <row r="29" spans="1:17" ht="22.1" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="13">
+        <v>128</v>
+      </c>
+      <c r="B29" s="15">
         <v>9.5</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="16">
         <v>9</v>
       </c>
-      <c r="D29" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="14">
+      <c r="D29" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="16">
         <v>2</v>
       </c>
       <c r="F29" s="1"/>
@@ -3899,18 +5006,18 @@
     </row>
     <row r="30" spans="1:17" ht="22.1" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="13">
+        <v>129</v>
+      </c>
+      <c r="B30" s="15">
         <v>5.8</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="16">
         <v>4</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" s="14">
+      <c r="D30" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="16">
         <v>3</v>
       </c>
       <c r="F30" s="1"/>
@@ -3928,18 +5035,18 @@
     </row>
     <row r="31" spans="1:17" ht="22.1" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="13">
+        <v>130</v>
+      </c>
+      <c r="B31" s="15">
         <v>7</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="16">
         <v>7</v>
       </c>
-      <c r="D31" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E31" s="14">
+      <c r="D31" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="16">
         <v>4</v>
       </c>
       <c r="F31" s="1"/>
@@ -3957,18 +5064,18 @@
     </row>
     <row r="32" spans="1:17" ht="22.1" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="13">
+        <v>131</v>
+      </c>
+      <c r="B32" s="15">
         <v>7.7</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="16">
         <v>10</v>
       </c>
-      <c r="D32" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="14">
+      <c r="D32" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="16">
         <v>3</v>
       </c>
       <c r="F32" s="1"/>
@@ -3986,18 +5093,18 @@
     </row>
     <row r="33" spans="1:17" ht="22.1" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" s="13">
+        <v>132</v>
+      </c>
+      <c r="B33" s="15">
         <v>9</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="16">
         <v>5</v>
       </c>
-      <c r="D33" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="14">
+      <c r="D33" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="16">
         <v>4</v>
       </c>
       <c r="F33" s="1"/>
@@ -4015,18 +5122,18 @@
     </row>
     <row r="34" spans="1:17" ht="22.1" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="13">
+        <v>133</v>
+      </c>
+      <c r="B34" s="15">
         <v>5.2</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="16">
         <v>8</v>
       </c>
-      <c r="D34" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="14">
+      <c r="D34" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="16">
         <v>2</v>
       </c>
       <c r="F34" s="1"/>
@@ -4044,18 +5151,18 @@
     </row>
     <row r="35" spans="1:17" ht="22.1" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B35" s="13">
+        <v>134</v>
+      </c>
+      <c r="B35" s="15">
         <v>6.5</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="16">
         <v>11</v>
       </c>
-      <c r="D35" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="14">
+      <c r="D35" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="16">
         <v>3</v>
       </c>
       <c r="F35" s="1"/>
@@ -4073,18 +5180,18 @@
     </row>
     <row r="36" spans="1:17" ht="22.1" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="13">
+        <v>135</v>
+      </c>
+      <c r="B36" s="15">
         <v>7.5</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="16">
         <v>6</v>
       </c>
-      <c r="D36" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" s="14">
+      <c r="D36" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="16">
         <v>2</v>
       </c>
       <c r="F36" s="1"/>
@@ -4102,18 +5209,18 @@
     </row>
     <row r="37" spans="1:17" ht="22.1" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B37" s="13">
+        <v>136</v>
+      </c>
+      <c r="B37" s="15">
         <v>8.5</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="16">
         <v>8</v>
       </c>
-      <c r="D37" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="14">
+      <c r="D37" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="16">
         <v>3</v>
       </c>
       <c r="F37" s="1"/>
@@ -4188,15 +5295,754 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="whole" sqref="E2:E37" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="whole" sqref="E2:E37" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>1</formula1>
       <formula2>4</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="C2:C37" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="whole" sqref="C2:C37" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>0</formula1>
       <formula2>12</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="5" width="22" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25" customHeight="1">
+      <c r="A2" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="17">
+        <v>6</v>
+      </c>
+      <c r="C2" s="17">
+        <v>5</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="17">
+        <v>2</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="25" customHeight="1">
+      <c r="A3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="17">
+        <v>8</v>
+      </c>
+      <c r="C3" s="17">
+        <v>9</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="17">
+        <v>4</v>
+      </c>
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="1:7" ht="25" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="17">
+        <v>7</v>
+      </c>
+      <c r="C4" s="17">
+        <v>8</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="25" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="17">
+        <v>5</v>
+      </c>
+      <c r="C5" s="17">
+        <v>6</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="17">
+        <v>2</v>
+      </c>
+      <c r="G5" s="21"/>
+    </row>
+    <row r="6" spans="1:7" ht="25" customHeight="1">
+      <c r="A6" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17">
+        <v>7</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3</v>
+      </c>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" ht="25" customHeight="1">
+      <c r="A7" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="17">
+        <v>7</v>
+      </c>
+      <c r="C7" s="17">
+        <v>0</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="17">
+        <v>1</v>
+      </c>
+      <c r="G7" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G4:G7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1">
+      <c r="A2" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="17">
+        <v>14</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1">
+      <c r="A3" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="17">
+        <v>12</v>
+      </c>
+      <c r="D3" s="21"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="17">
+        <v>10</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="D5" s="21"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="D7" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="7" width="22" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="25" customHeight="1">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17">
+        <v>1</v>
+      </c>
+      <c r="D2" s="17">
+        <v>1</v>
+      </c>
+      <c r="E2" s="17">
+        <v>1</v>
+      </c>
+      <c r="F2" s="17">
+        <v>4</v>
+      </c>
+      <c r="G2" s="17">
+        <v>1</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="25" customHeight="1">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17">
+        <v>2</v>
+      </c>
+      <c r="C3" s="17">
+        <v>3</v>
+      </c>
+      <c r="D3" s="17">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17">
+        <v>6</v>
+      </c>
+      <c r="F3" s="17">
+        <v>4</v>
+      </c>
+      <c r="G3" s="17">
+        <v>3</v>
+      </c>
+      <c r="I3" s="21"/>
+    </row>
+    <row r="4" spans="1:9" ht="25" customHeight="1">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17">
+        <v>4</v>
+      </c>
+      <c r="C4" s="17">
+        <v>10</v>
+      </c>
+      <c r="D4" s="17">
+        <v>2</v>
+      </c>
+      <c r="E4" s="17">
+        <v>10</v>
+      </c>
+      <c r="F4" s="17">
+        <v>4</v>
+      </c>
+      <c r="G4" s="17">
+        <v>8</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="25" customHeight="1">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17">
+        <v>7</v>
+      </c>
+      <c r="C5" s="17">
+        <v>8</v>
+      </c>
+      <c r="D5" s="17">
+        <v>3</v>
+      </c>
+      <c r="E5" s="17">
+        <v>4</v>
+      </c>
+      <c r="F5" s="17">
+        <v>4</v>
+      </c>
+      <c r="G5" s="17">
+        <v>9</v>
+      </c>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" ht="25" customHeight="1">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17">
+        <v>10</v>
+      </c>
+      <c r="C6" s="17">
+        <v>5</v>
+      </c>
+      <c r="D6" s="17">
+        <v>5</v>
+      </c>
+      <c r="E6" s="17">
+        <v>1</v>
+      </c>
+      <c r="F6" s="17">
+        <v>4</v>
+      </c>
+      <c r="G6" s="17">
+        <v>4</v>
+      </c>
+      <c r="I6" s="21"/>
+    </row>
+    <row r="7" spans="1:9" ht="25" customHeight="1">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17">
+        <v>7</v>
+      </c>
+      <c r="C7" s="17">
+        <v>3</v>
+      </c>
+      <c r="D7" s="17">
+        <v>8</v>
+      </c>
+      <c r="E7" s="17">
+        <v>4</v>
+      </c>
+      <c r="F7" s="17">
+        <v>4</v>
+      </c>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="I7" s="21"/>
+    </row>
+    <row r="8" spans="1:9" ht="25" customHeight="1">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17">
+        <v>4</v>
+      </c>
+      <c r="C8" s="17">
+        <v>2</v>
+      </c>
+      <c r="D8" s="17">
+        <v>10</v>
+      </c>
+      <c r="E8" s="17">
+        <v>10</v>
+      </c>
+      <c r="F8" s="17">
+        <v>4</v>
+      </c>
+      <c r="G8" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="25" customHeight="1">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17">
+        <v>1</v>
+      </c>
+      <c r="D9" s="17">
+        <v>3</v>
+      </c>
+      <c r="E9" s="17">
+        <v>6</v>
+      </c>
+      <c r="F9" s="17">
+        <v>4</v>
+      </c>
+      <c r="G9" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="25" customHeight="1">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17">
+        <v>1</v>
+      </c>
+      <c r="C10" s="17">
+        <v>1</v>
+      </c>
+      <c r="D10" s="17">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17">
+        <v>1</v>
+      </c>
+      <c r="F10" s="17">
+        <v>4</v>
+      </c>
+      <c r="G10" s="17">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I4:I7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="3" width="22" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1">
+      <c r="A2" s="17">
+        <v>0</v>
+      </c>
+      <c r="B2" s="17">
+        <v>15</v>
+      </c>
+      <c r="C2" s="17">
+        <v>0</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1">
+      <c r="A3" s="17">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17">
+        <v>0</v>
+      </c>
+      <c r="E3" s="21"/>
+    </row>
+    <row r="4" spans="1:5" ht="25" customHeight="1">
+      <c r="A4" s="17">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
+        <v>4</v>
+      </c>
+      <c r="C4" s="17">
+        <v>0</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25" customHeight="1">
+      <c r="A5" s="17">
+        <v>3</v>
+      </c>
+      <c r="B5" s="17">
+        <v>3</v>
+      </c>
+      <c r="C5" s="17">
+        <v>1</v>
+      </c>
+      <c r="E5" s="21"/>
+    </row>
+    <row r="6" spans="1:5" ht="25" customHeight="1">
+      <c r="A6" s="17">
+        <v>4</v>
+      </c>
+      <c r="B6" s="17">
+        <v>2</v>
+      </c>
+      <c r="C6" s="17">
+        <v>1</v>
+      </c>
+      <c r="E6" s="21"/>
+    </row>
+    <row r="7" spans="1:5" ht="25" customHeight="1">
+      <c r="A7" s="17">
+        <v>5</v>
+      </c>
+      <c r="B7" s="17">
+        <v>1</v>
+      </c>
+      <c r="C7" s="17">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21"/>
+    </row>
+    <row r="8" spans="1:5" ht="25" customHeight="1">
+      <c r="A8" s="17">
+        <v>6</v>
+      </c>
+      <c r="B8" s="17">
+        <v>1</v>
+      </c>
+      <c r="C8" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="25" customHeight="1">
+      <c r="A9" s="17">
+        <v>7</v>
+      </c>
+      <c r="B9" s="17">
+        <v>1</v>
+      </c>
+      <c r="C9" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="25" customHeight="1">
+      <c r="A10" s="17">
+        <v>8</v>
+      </c>
+      <c r="B10" s="17">
+        <v>1</v>
+      </c>
+      <c r="C10" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="25" customHeight="1">
+      <c r="A11" s="17">
+        <v>9</v>
+      </c>
+      <c r="B11" s="17">
+        <v>1</v>
+      </c>
+      <c r="C11" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="25" customHeight="1">
+      <c r="A12" s="17">
+        <v>10</v>
+      </c>
+      <c r="B12" s="17">
+        <v>0</v>
+      </c>
+      <c r="C12" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="25" customHeight="1">
+      <c r="A13" s="17">
+        <v>11</v>
+      </c>
+      <c r="B13" s="17">
+        <v>0</v>
+      </c>
+      <c r="C13" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="25" customHeight="1">
+      <c r="A14" s="17">
+        <v>12</v>
+      </c>
+      <c r="B14" s="17">
+        <v>0</v>
+      </c>
+      <c r="C14" s="17">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="17">
+        <v>12</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="17">
+        <v>14</v>
+      </c>
+      <c r="C3" s="21"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="17">
+        <v>14</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="17">
+        <v>18</v>
+      </c>
+      <c r="C5" s="21"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="17">
+        <v>21</v>
+      </c>
+      <c r="C6" s="21"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1">
+      <c r="A7" s="17">
+        <v>23</v>
+      </c>
+      <c r="C7" s="21"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1">
+      <c r="A8" s="17">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1">
+      <c r="A9" s="17">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/kapitola_02.xlsx
+++ b/data/kapitola_02.xlsx
@@ -2,15 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R Projects\github\statistics-for-psychology\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73AE155-EF1B-484F-92CF-6DF8C0697109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEA1F8D1-3BBE-49ED-9F4A-02E7D95D2377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{C54D4CCB-121D-459E-97E4-06E46F5BB724}"/>
   </bookViews>
   <sheets>
     <sheet name="Prehled" sheetId="1" r:id="rId1"/>
@@ -32,6 +27,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -43,6 +41,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -50,6 +51,435 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="179">
   <si>
+    <t>Odpočatost před úlohou</t>
+  </si>
+  <si>
+    <t>Platné odpovědi n</t>
+  </si>
+  <si>
+    <t>Kód</t>
+  </si>
+  <si>
+    <t>Odpočatost</t>
+  </si>
+  <si>
+    <t>Četnost</t>
+  </si>
+  <si>
+    <t>Podíl</t>
+  </si>
+  <si>
+    <t>Procenta</t>
+  </si>
+  <si>
+    <t>Kumul. počet</t>
+  </si>
+  <si>
+    <t>Kumul. podíl</t>
+  </si>
+  <si>
+    <t>Kumul. %</t>
+  </si>
+  <si>
+    <t>Vůbec</t>
+  </si>
+  <si>
+    <t>Trochu</t>
+  </si>
+  <si>
+    <t>Dost</t>
+  </si>
+  <si>
+    <t>Zcela</t>
+  </si>
+  <si>
+    <t>Celkem</t>
+  </si>
+  <si>
+    <t>Počítáme 36 modelových účastníků. Odpočatost má čtyři uspořádané kategorie.</t>
+  </si>
+  <si>
+    <t>Podíly se počítají z nezkrácených hodnot. Kumulativní sloupce už nesčítáme.</t>
+  </si>
+  <si>
+    <t>Zkuste změnit Data!E2 z 2 na 3 a sledujte tabulku i graf. Potom obnovte 2.</t>
+  </si>
+  <si>
+    <t>Doba spánku: intervalové četnosti</t>
+  </si>
+  <si>
+    <t>Platné údaje n</t>
+  </si>
+  <si>
+    <t>Dolní mez</t>
+  </si>
+  <si>
+    <t>Horní mez</t>
+  </si>
+  <si>
+    <t>Interval (h)</t>
+  </si>
+  <si>
+    <t>&gt; 4 až 5</t>
+  </si>
+  <si>
+    <t>&gt; 5 až 6</t>
+  </si>
+  <si>
+    <t>&gt; 6 až 7</t>
+  </si>
+  <si>
+    <t>&gt; 7 až 8</t>
+  </si>
+  <si>
+    <t>&gt; 8 až 9</t>
+  </si>
+  <si>
+    <t>&gt; 9 až 10</t>
+  </si>
+  <si>
+    <t>Dolní mez nepatří do intervalu, horní ano. Intervaly mají šířku 1 hodina.</t>
+  </si>
+  <si>
+    <t>Tři z 36 účastníků spánek neuvedli. Prázdná buňka neznamená 0 hodin.</t>
+  </si>
+  <si>
+    <t>Zkuste změnit Data!B2 z 6 na 7. Po ověření přesunu obnovte hodnotu 6.</t>
+  </si>
+  <si>
+    <t>Při rozšíření dat upravte oblasti ve vzorcích a pokrytí intervaly.</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>spanek_h</t>
+  </si>
+  <si>
+    <t>slova</t>
+  </si>
+  <si>
+    <t>cast_dne</t>
+  </si>
+  <si>
+    <t>odpocatost</t>
+  </si>
+  <si>
+    <t>P01</t>
+  </si>
+  <si>
+    <t>dopoledne</t>
+  </si>
+  <si>
+    <t>P02</t>
+  </si>
+  <si>
+    <t>odpoledne</t>
+  </si>
+  <si>
+    <t>P03</t>
+  </si>
+  <si>
+    <t>P04</t>
+  </si>
+  <si>
+    <t>P05</t>
+  </si>
+  <si>
+    <t>P06</t>
+  </si>
+  <si>
+    <t>P07</t>
+  </si>
+  <si>
+    <t>P08</t>
+  </si>
+  <si>
+    <t>P09</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>P13</t>
+  </si>
+  <si>
+    <t>P14</t>
+  </si>
+  <si>
+    <t>P15</t>
+  </si>
+  <si>
+    <t>P16</t>
+  </si>
+  <si>
+    <t>P17</t>
+  </si>
+  <si>
+    <t>P18</t>
+  </si>
+  <si>
+    <t>P19</t>
+  </si>
+  <si>
+    <t>P20</t>
+  </si>
+  <si>
+    <t>P21</t>
+  </si>
+  <si>
+    <t>P22</t>
+  </si>
+  <si>
+    <t>P23</t>
+  </si>
+  <si>
+    <t>P24</t>
+  </si>
+  <si>
+    <t>P25</t>
+  </si>
+  <si>
+    <t>P26</t>
+  </si>
+  <si>
+    <t>P27</t>
+  </si>
+  <si>
+    <t>P28</t>
+  </si>
+  <si>
+    <t>P29</t>
+  </si>
+  <si>
+    <t>P30</t>
+  </si>
+  <si>
+    <t>P31</t>
+  </si>
+  <si>
+    <t>P32</t>
+  </si>
+  <si>
+    <t>P33</t>
+  </si>
+  <si>
+    <t>P34</t>
+  </si>
+  <si>
+    <t>P35</t>
+  </si>
+  <si>
+    <t>P36</t>
+  </si>
+  <si>
+    <t>Modelová data vytvořená pro výuku; nejde o skutečný výzkum.</t>
+  </si>
+  <si>
+    <t>Jeden řádek = jeden účastník při jedné návštěvě. Všichni plní úlohu v tichu.</t>
+  </si>
+  <si>
+    <t>spanek_h: odhad skutečného spánku předchozí noci v hodinách (0 až 24).</t>
+  </si>
+  <si>
+    <t>Prázdná buňka znamená neuvedený spánek (P05, P11, P24).</t>
+  </si>
+  <si>
+    <t>slova: počet různých správně vybavených slov z 12; jedna minuta na čtení</t>
+  </si>
+  <si>
+    <t>a jedna na vybavení. Nula je platný výsledek, nikoli chybějící údaj.</t>
+  </si>
+  <si>
+    <t>cast_dne: dopoledne před 12:00, odpoledne od 12:00.</t>
+  </si>
+  <si>
+    <t>odpocatost: Jak odpočatě se právě cítíte? Odpověď před úlohou.</t>
+  </si>
+  <si>
+    <t>1 = vůbec, 2 = trochu, 3 = dost, 4 = zcela.</t>
+  </si>
+  <si>
+    <t>Změny čísel v původních 36 řádcích se promítnou do tabulek a grafů.</t>
+  </si>
+  <si>
+    <t>Při přidání dalších řádků je potřeba rozšířit oblasti ve vzorcích.</t>
+  </si>
+  <si>
+    <t>Použití a původ</t>
+  </si>
+  <si>
+    <t>Úvodní příklad, jmenovatel procent</t>
+  </si>
+  <si>
+    <t>Autorské ilustrační údaje. Nejde o skutečný výzkum.</t>
+  </si>
+  <si>
+    <t>Strategie</t>
+  </si>
+  <si>
+    <t>Procvičování</t>
+  </si>
+  <si>
+    <t>Čtení</t>
+  </si>
+  <si>
+    <t>Vysvětlování</t>
+  </si>
+  <si>
+    <t>Výsečový a sloupcový graf</t>
+  </si>
+  <si>
+    <t>Hodnota</t>
+  </si>
+  <si>
+    <t>Souměrnost</t>
+  </si>
+  <si>
+    <t>Šikmost doprava</t>
+  </si>
+  <si>
+    <t>Šikmost doleva</t>
+  </si>
+  <si>
+    <t>Dva vrcholy</t>
+  </si>
+  <si>
+    <t>Rovnoměrnost</t>
+  </si>
+  <si>
+    <t>Odlehlost</t>
+  </si>
+  <si>
+    <t>Obrázek: šest tvarů rozdělení</t>
+  </si>
+  <si>
+    <t>Autorské schematické četnosti. Sloupce představují šest různých rozdělení, nikoli spárovaná měření lidí.</t>
+  </si>
+  <si>
+    <t>Počet správných odpovědí</t>
+  </si>
+  <si>
+    <t>Podlaha: četnost</t>
+  </si>
+  <si>
+    <t>Strop: četnost</t>
+  </si>
+  <si>
+    <t>Obrázek: meze nástroje</t>
+  </si>
+  <si>
+    <t>Doba (s)</t>
+  </si>
+  <si>
+    <t>Výklad: stonek a list</t>
+  </si>
+  <si>
+    <t>Odpočatost (kód 1–4)</t>
+  </si>
+  <si>
+    <t>Cvičení 1 a 2</t>
+  </si>
+  <si>
+    <t>Autorské údaje. 1 vůbec, 2 trochu, 3 dost, 4 zcela.</t>
+  </si>
+  <si>
+    <t>Odpověď</t>
+  </si>
+  <si>
+    <t>Ano</t>
+  </si>
+  <si>
+    <t>Ne</t>
+  </si>
+  <si>
+    <t>Chybí</t>
+  </si>
+  <si>
+    <t>Cvičení 3a</t>
+  </si>
+  <si>
+    <t>Zadáno 25 oslovených; 20 odpovědělo. Četnosti, nikoli jednotliví lidé.</t>
+  </si>
+  <si>
+    <t>Možnost</t>
+  </si>
+  <si>
+    <t>Počet označení</t>
+  </si>
+  <si>
+    <t>Počet odpovídajících</t>
+  </si>
+  <si>
+    <t>Hluk</t>
+  </si>
+  <si>
+    <t>Telefon</t>
+  </si>
+  <si>
+    <t>Únava</t>
+  </si>
+  <si>
+    <t>Cvičení 3b</t>
+  </si>
+  <si>
+    <t>Bylo možné označit více možností. Překryvy mezi lidmi nejsou zadány.</t>
+  </si>
+  <si>
+    <t>Počet chyb</t>
+  </si>
+  <si>
+    <t>Cvičení 4</t>
+  </si>
+  <si>
+    <t>Spánek (h)</t>
+  </si>
+  <si>
+    <t>Cvičení 5</t>
+  </si>
+  <si>
+    <t>Intervaly: více než 4 až 5 včetně, více než 5 až 6 včetně, více než 6 až 7 včetně, více než 7 až 8 včetně.</t>
+  </si>
+  <si>
+    <t>Stonek</t>
+  </si>
+  <si>
+    <t>Listy</t>
+  </si>
+  <si>
+    <t>1 3 3 8</t>
+  </si>
+  <si>
+    <t>0 5</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Cvičení 8: zadání k rekonstrukci</t>
+  </si>
+  <si>
+    <t>Klíč: 2 | 3 znamená 23 sekund. Sloupec Listy je záměrně textový zápis zadání, nikoli hotové řešení.</t>
+  </si>
+  <si>
+    <t>Skupina</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Zavádějící graf; cvičení 9</t>
+  </si>
+  <si>
     <t>Data ke kapitole 2</t>
   </si>
   <si>
@@ -80,99 +510,57 @@
     <t>A2:E7</t>
   </si>
   <si>
-    <t>Úvodní příklad, jmenovatel procent</t>
-  </si>
-  <si>
-    <t>Strategie</t>
-  </si>
-  <si>
     <t>A2:B4</t>
   </si>
   <si>
-    <t>Výsečový a sloupcový graf</t>
-  </si>
-  <si>
     <t>Tvary</t>
   </si>
   <si>
     <t>A2:G10</t>
   </si>
   <si>
-    <t>Obrázek: šest tvarů rozdělení</t>
-  </si>
-  <si>
     <t>Podlaha_strop</t>
   </si>
   <si>
     <t>A2:C14</t>
   </si>
   <si>
-    <t>Obrázek: meze nástroje</t>
-  </si>
-  <si>
-    <t>Stonek</t>
-  </si>
-  <si>
     <t>A2:A9</t>
   </si>
   <si>
-    <t>Výklad: stonek a list</t>
-  </si>
-  <si>
     <t>U01_odpocatost</t>
   </si>
   <si>
     <t>A2:A13</t>
   </si>
   <si>
-    <t>Cvičení 1 a 2</t>
-  </si>
-  <si>
     <t>U03_chybeni</t>
   </si>
   <si>
-    <t>Cvičení 3a</t>
-  </si>
-  <si>
     <t>U03_ruseni</t>
   </si>
   <si>
     <t>A2:C4</t>
   </si>
   <si>
-    <t>Cvičení 3b</t>
-  </si>
-  <si>
     <t>U04_chyby</t>
   </si>
   <si>
     <t>A2:A11</t>
   </si>
   <si>
-    <t>Cvičení 4</t>
-  </si>
-  <si>
     <t>U05_spanek</t>
   </si>
   <si>
-    <t>Cvičení 5</t>
-  </si>
-  <si>
     <t>U08_stonek</t>
   </si>
   <si>
-    <t>Cvičení 8: zadání k rekonstrukci</t>
-  </si>
-  <si>
     <t>Podpora</t>
   </si>
   <si>
     <t>A2:C3</t>
   </si>
   <si>
-    <t>Zavádějící graf; cvičení 9</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
@@ -198,393 +586,6 @@
   </si>
   <si>
     <t>Hotové intervalové četnosti a histogram</t>
-  </si>
-  <si>
-    <t>Odpočatost před úlohou</t>
-  </si>
-  <si>
-    <t>Platné odpovědi n</t>
-  </si>
-  <si>
-    <t>Kód</t>
-  </si>
-  <si>
-    <t>Odpočatost</t>
-  </si>
-  <si>
-    <t>Četnost</t>
-  </si>
-  <si>
-    <t>Podíl</t>
-  </si>
-  <si>
-    <t>Procenta</t>
-  </si>
-  <si>
-    <t>Kumul. počet</t>
-  </si>
-  <si>
-    <t>Kumul. podíl</t>
-  </si>
-  <si>
-    <t>Kumul. %</t>
-  </si>
-  <si>
-    <t>Vůbec</t>
-  </si>
-  <si>
-    <t>Trochu</t>
-  </si>
-  <si>
-    <t>Dost</t>
-  </si>
-  <si>
-    <t>Zcela</t>
-  </si>
-  <si>
-    <t>Celkem</t>
-  </si>
-  <si>
-    <t>Počítáme 36 modelových účastníků. Odpočatost má čtyři uspořádané kategorie.</t>
-  </si>
-  <si>
-    <t>Podíly se počítají z nezkrácených hodnot. Kumulativní sloupce už nesčítáme.</t>
-  </si>
-  <si>
-    <t>Zkuste změnit Data!E2 z 2 na 3 a sledujte tabulku i graf. Potom obnovte 2.</t>
-  </si>
-  <si>
-    <t>Doba spánku: intervalové četnosti</t>
-  </si>
-  <si>
-    <t>Platné údaje n</t>
-  </si>
-  <si>
-    <t>Dolní mez</t>
-  </si>
-  <si>
-    <t>Horní mez</t>
-  </si>
-  <si>
-    <t>Interval (h)</t>
-  </si>
-  <si>
-    <t>&gt; 4 až 5</t>
-  </si>
-  <si>
-    <t>&gt; 5 až 6</t>
-  </si>
-  <si>
-    <t>&gt; 6 až 7</t>
-  </si>
-  <si>
-    <t>&gt; 7 až 8</t>
-  </si>
-  <si>
-    <t>&gt; 8 až 9</t>
-  </si>
-  <si>
-    <t>&gt; 9 až 10</t>
-  </si>
-  <si>
-    <t>Dolní mez nepatří do intervalu, horní ano. Intervaly mají šířku 1 hodina.</t>
-  </si>
-  <si>
-    <t>Tři z 36 účastníků spánek neuvedli. Prázdná buňka neznamená 0 hodin.</t>
-  </si>
-  <si>
-    <t>Zkuste změnit Data!B2 z 6 na 7. Po ověření přesunu obnovte hodnotu 6.</t>
-  </si>
-  <si>
-    <t>Při rozšíření dat upravte oblasti ve vzorcích a pokrytí intervaly.</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>spanek_h</t>
-  </si>
-  <si>
-    <t>slova</t>
-  </si>
-  <si>
-    <t>cast_dne</t>
-  </si>
-  <si>
-    <t>odpocatost</t>
-  </si>
-  <si>
-    <t>Modelová data vytvořená pro výuku; nejde o skutečný výzkum.</t>
-  </si>
-  <si>
-    <t>P01</t>
-  </si>
-  <si>
-    <t>dopoledne</t>
-  </si>
-  <si>
-    <t>P02</t>
-  </si>
-  <si>
-    <t>odpoledne</t>
-  </si>
-  <si>
-    <t>Jeden řádek = jeden účastník při jedné návštěvě. Všichni plní úlohu v tichu.</t>
-  </si>
-  <si>
-    <t>P03</t>
-  </si>
-  <si>
-    <t>spanek_h: odhad skutečného spánku předchozí noci v hodinách (0 až 24).</t>
-  </si>
-  <si>
-    <t>P04</t>
-  </si>
-  <si>
-    <t>Prázdná buňka znamená neuvedený spánek (P05, P11, P24).</t>
-  </si>
-  <si>
-    <t>P05</t>
-  </si>
-  <si>
-    <t>slova: počet různých správně vybavených slov z 12; jedna minuta na čtení</t>
-  </si>
-  <si>
-    <t>P06</t>
-  </si>
-  <si>
-    <t>a jedna na vybavení. Nula je platný výsledek, nikoli chybějící údaj.</t>
-  </si>
-  <si>
-    <t>P07</t>
-  </si>
-  <si>
-    <t>cast_dne: dopoledne před 12:00, odpoledne od 12:00.</t>
-  </si>
-  <si>
-    <t>P08</t>
-  </si>
-  <si>
-    <t>odpocatost: Jak odpočatě se právě cítíte? Odpověď před úlohou.</t>
-  </si>
-  <si>
-    <t>P09</t>
-  </si>
-  <si>
-    <t>1 = vůbec, 2 = trochu, 3 = dost, 4 = zcela.</t>
-  </si>
-  <si>
-    <t>P10</t>
-  </si>
-  <si>
-    <t>Změny čísel v původních 36 řádcích se promítnou do tabulek a grafů.</t>
-  </si>
-  <si>
-    <t>P11</t>
-  </si>
-  <si>
-    <t>Při přidání dalších řádků je potřeba rozšířit oblasti ve vzorcích.</t>
-  </si>
-  <si>
-    <t>P12</t>
-  </si>
-  <si>
-    <t>P13</t>
-  </si>
-  <si>
-    <t>P14</t>
-  </si>
-  <si>
-    <t>P15</t>
-  </si>
-  <si>
-    <t>P16</t>
-  </si>
-  <si>
-    <t>P17</t>
-  </si>
-  <si>
-    <t>P18</t>
-  </si>
-  <si>
-    <t>P19</t>
-  </si>
-  <si>
-    <t>P20</t>
-  </si>
-  <si>
-    <t>P21</t>
-  </si>
-  <si>
-    <t>P22</t>
-  </si>
-  <si>
-    <t>P23</t>
-  </si>
-  <si>
-    <t>P24</t>
-  </si>
-  <si>
-    <t>P25</t>
-  </si>
-  <si>
-    <t>P26</t>
-  </si>
-  <si>
-    <t>P27</t>
-  </si>
-  <si>
-    <t>P28</t>
-  </si>
-  <si>
-    <t>P29</t>
-  </si>
-  <si>
-    <t>P30</t>
-  </si>
-  <si>
-    <t>P31</t>
-  </si>
-  <si>
-    <t>P32</t>
-  </si>
-  <si>
-    <t>P33</t>
-  </si>
-  <si>
-    <t>P34</t>
-  </si>
-  <si>
-    <t>P35</t>
-  </si>
-  <si>
-    <t>P36</t>
-  </si>
-  <si>
-    <t>Použití a původ</t>
-  </si>
-  <si>
-    <t>Autorské ilustrační údaje. Nejde o skutečný výzkum.</t>
-  </si>
-  <si>
-    <t>Procvičování</t>
-  </si>
-  <si>
-    <t>Čtení</t>
-  </si>
-  <si>
-    <t>Vysvětlování</t>
-  </si>
-  <si>
-    <t>Hodnota</t>
-  </si>
-  <si>
-    <t>Souměrnost</t>
-  </si>
-  <si>
-    <t>Šikmost doprava</t>
-  </si>
-  <si>
-    <t>Šikmost doleva</t>
-  </si>
-  <si>
-    <t>Dva vrcholy</t>
-  </si>
-  <si>
-    <t>Rovnoměrnost</t>
-  </si>
-  <si>
-    <t>Odlehlost</t>
-  </si>
-  <si>
-    <t>Autorské schematické četnosti. Sloupce představují šest různých rozdělení, nikoli spárovaná měření lidí.</t>
-  </si>
-  <si>
-    <t>Počet správných odpovědí</t>
-  </si>
-  <si>
-    <t>Podlaha: četnost</t>
-  </si>
-  <si>
-    <t>Strop: četnost</t>
-  </si>
-  <si>
-    <t>Doba (s)</t>
-  </si>
-  <si>
-    <t>Odpočatost (kód 1–4)</t>
-  </si>
-  <si>
-    <t>Autorské údaje. 1 vůbec, 2 trochu, 3 dost, 4 zcela.</t>
-  </si>
-  <si>
-    <t>Odpověď</t>
-  </si>
-  <si>
-    <t>Ano</t>
-  </si>
-  <si>
-    <t>Ne</t>
-  </si>
-  <si>
-    <t>Chybí</t>
-  </si>
-  <si>
-    <t>Zadáno 25 oslovených; 20 odpovědělo. Četnosti, nikoli jednotliví lidé.</t>
-  </si>
-  <si>
-    <t>Možnost</t>
-  </si>
-  <si>
-    <t>Počet označení</t>
-  </si>
-  <si>
-    <t>Počet odpovídajících</t>
-  </si>
-  <si>
-    <t>Hluk</t>
-  </si>
-  <si>
-    <t>Telefon</t>
-  </si>
-  <si>
-    <t>Únava</t>
-  </si>
-  <si>
-    <t>Bylo možné označit více možností. Překryvy mezi lidmi nejsou zadány.</t>
-  </si>
-  <si>
-    <t>Počet chyb</t>
-  </si>
-  <si>
-    <t>Spánek (h)</t>
-  </si>
-  <si>
-    <t>Intervaly: více než 4 až 5 včetně, více než 5 až 6 včetně, více než 6 až 7 včetně, více než 7 až 8 včetně.</t>
-  </si>
-  <si>
-    <t>Listy</t>
-  </si>
-  <si>
-    <t>1 3 3 8</t>
-  </si>
-  <si>
-    <t>0 5</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Klíč: 2 | 3 znamená 23 sekund. Sloupec Listy je záměrně textový zápis zadání, nikoli hotové řešení.</t>
-  </si>
-  <si>
-    <t>Skupina</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
 </sst>
 </file>
@@ -596,54 +597,68 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF223744"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF223744"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color rgb="FF223744"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF223744"/>
-      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF526775"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF526775"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF223744"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="6">
@@ -656,21 +671,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF234F62"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEFF6FA"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF8E7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF1CB"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -683,78 +702,91 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+  <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -775,7 +807,14 @@
   <c:date1904 val="0"/>
   <c:lang val="cs-CZ"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -783,12 +822,11 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500"/>
+            </a:pPr>
             <a:r>
-              <a:rPr sz="1125">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
+              <a:rPr lang="cs-CZ"/>
               <a:t>Odpočatost</a:t>
             </a:r>
           </a:p>
@@ -858,7 +896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D822-41B8-9D4B-67F4E0AE0A1D}"/>
+              <c16:uniqueId val="{00000001-9469-4484-A970-ED8D45410F73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -871,33 +909,27 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
+        <c:axId val="1323916080"/>
+        <c:axId val="1636152560"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48650112"/>
+        <c:axId val="1323916080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
               <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
                 <a:r>
+                  <a:rPr lang="cs-CZ"/>
                   <a:t>Odpočatost</a:t>
                 </a:r>
               </a:p>
@@ -906,55 +938,36 @@
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="825">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="cs-CZ"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48672768"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="1636152560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48672768"/>
+        <c:axId val="1636152560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
+        <c:majorGridlines/>
         <c:title>
           <c:tx>
             <c:rich>
               <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
                 <a:r>
+                  <a:rPr lang="cs-CZ"/>
                   <a:t>Počet účastníků</a:t>
                 </a:r>
               </a:p>
@@ -963,40 +976,39 @@
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="825">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="cs-CZ"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48650112"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="1323916080"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
-  <c:spPr>
-    <a:ln w="9525">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1100">
+          <a:latin typeface="Arial"/>
+          <a:ea typeface="Arial"/>
+          <a:cs typeface="Arial"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="cs-CZ"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1010,7 +1022,14 @@
   <c:date1904 val="0"/>
   <c:lang val="cs-CZ"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1018,12 +1037,11 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500"/>
+            </a:pPr>
             <a:r>
-              <a:rPr sz="1125">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
+              <a:rPr lang="cs-CZ"/>
               <a:t>Doba spánku</a:t>
             </a:r>
           </a:p>
@@ -1105,7 +1123,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5417-431E-B3D1-D106FC7FDDBC}"/>
+              <c16:uniqueId val="{00000001-A1DD-4D10-BA9C-E92FC05DBF41}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1118,33 +1136,27 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="0"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
+        <c:axId val="1323913760"/>
+        <c:axId val="1636155920"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48650112"/>
+        <c:axId val="1323913760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
               <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
                 <a:r>
+                  <a:rPr lang="cs-CZ"/>
                   <a:t>Doba spánku (h)</a:t>
                 </a:r>
               </a:p>
@@ -1153,55 +1165,36 @@
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="825">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="cs-CZ"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48672768"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="1636155920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48672768"/>
+        <c:axId val="1636155920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
+        <c:majorGridlines/>
         <c:title>
           <c:tx>
             <c:rich>
               <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
                 <a:r>
+                  <a:rPr lang="cs-CZ"/>
                   <a:t>Počet účastníků</a:t>
                 </a:r>
               </a:p>
@@ -1210,40 +1203,39 @@
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:txPr>
-          <a:bodyPr anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="825">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="cs-CZ"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48650112"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="1323913760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
-  <c:spPr>
-    <a:ln w="9525">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1100">
+          <a:latin typeface="Arial"/>
+          <a:ea typeface="Arial"/>
+          <a:cs typeface="Arial"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="cs-CZ"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1257,7 +1249,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -1269,10 +1261,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart">
+        <xdr:cNvPr id="2" name="Graf 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16B0248A-B727-12AA-2FF0-F94893E0A4AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1310,10 +1302,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart">
+        <xdr:cNvPr id="2" name="Graf 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC19CAA1-66CF-089F-5764-F42402F70477}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1335,9 +1327,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office">
   <a:themeElements>
-    <a:clrScheme name="ChatGPT">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1377,68 +1369,162 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="ChatGPT">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
-                <a:lumMod val="102000"/>
-                <a:satMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:lumMod val="100000"/>
-                <a:satMod val="110000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1446,23 +1532,26 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1474,7 +1563,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1492,22 +1581,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
-                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1522,247 +1611,272 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E6CEAF-5F8D-44D4-8DE2-69D972866C1C}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="70" customWidth="1"/>
+    <col min="1" max="2" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="70.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-    </row>
-    <row r="2" spans="1:3" ht="30.1" customHeight="1">
+    <row r="1" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="2" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-    </row>
-    <row r="4" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A4" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-    </row>
-    <row r="5" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A5" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-    </row>
-    <row r="6" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A6" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-    </row>
-    <row r="7" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="30.1" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="30.1" customHeight="1">
+    <row r="3" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+    </row>
+    <row r="4" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+    </row>
+    <row r="5" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+    </row>
+    <row r="6" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+    </row>
+    <row r="7" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" ht="30.1" customHeight="1">
+    <row r="24" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" ht="30.1" customHeight="1">
+    <row r="25" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1775,94 +1889,94 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:C6"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C23EAE-9C6B-4558-9C4E-EA003711BCA4}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1">
-      <c r="A2" s="17">
+    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="25" customHeight="1">
-      <c r="A3" s="17">
+      <c r="C2" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
         <v>3</v>
       </c>
-      <c r="C3" s="21"/>
-    </row>
-    <row r="4" spans="1:3" ht="25" customHeight="1">
-      <c r="A4" s="17">
+      <c r="C3" s="22"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
         <v>2</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="25" customHeight="1">
-      <c r="A5" s="17">
+      <c r="C4" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
         <v>1</v>
       </c>
-      <c r="C5" s="21"/>
-    </row>
-    <row r="6" spans="1:3" ht="25" customHeight="1">
-      <c r="A6" s="17">
+      <c r="C5" s="22"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
         <v>4</v>
       </c>
-      <c r="C6" s="21"/>
-    </row>
-    <row r="7" spans="1:3" ht="25" customHeight="1">
-      <c r="A7" s="17">
+      <c r="C6" s="22"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
         <v>3</v>
       </c>
-      <c r="C7" s="21"/>
-    </row>
-    <row r="8" spans="1:3" ht="25" customHeight="1">
-      <c r="A8" s="17">
+      <c r="C7" s="22"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="25" customHeight="1">
-      <c r="A9" s="17">
+    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="25" customHeight="1">
-      <c r="A10" s="17">
+    <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="25" customHeight="1">
-      <c r="A11" s="17">
+    <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="25" customHeight="1">
-      <c r="A12" s="17">
+    <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="25" customHeight="1">
-      <c r="A13" s="17">
+    <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
         <v>2</v>
       </c>
     </row>
@@ -1871,234 +1985,234 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589E28B5-B248-4DC9-97BD-0B7E54EEAB8E}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="22" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="1" max="2" width="22.625" customWidth="1"/>
+    <col min="4" max="4" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="25" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B2" s="17">
+    <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="20">
         <v>9</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="25" customHeight="1">
-      <c r="A3" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="17">
+      <c r="D2" s="23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="20">
         <v>11</v>
       </c>
-      <c r="D3" s="21"/>
-    </row>
-    <row r="4" spans="1:4" ht="25" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="17">
+      <c r="D3" s="22"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="20">
         <v>5</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="D5" s="21"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="D7" s="21"/>
+      <c r="D4" s="23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" s="22"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="D4:D7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33258020-4CDD-4B1E-A5E1-DF83B18D13A4}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="1" max="3" width="22.625" customWidth="1"/>
+    <col min="5" max="5" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="25" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B2" s="17">
+    <row r="1" spans="1:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="20">
         <v>12</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="20">
         <v>20</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="25" customHeight="1">
-      <c r="A3" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="B3" s="17">
+      <c r="E2" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="20">
         <v>14</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="20">
         <v>20</v>
       </c>
-      <c r="E3" s="21"/>
-    </row>
-    <row r="4" spans="1:5" ht="25" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" s="17">
+      <c r="E3" s="22"/>
+    </row>
+    <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="20">
         <v>6</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="20">
         <v>20</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="E5" s="21"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="E6" s="21"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="E7" s="21"/>
+      <c r="E4" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFC7E-B9B1-4F3C-8B3A-022450CCC88F}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1">
-      <c r="A2" s="17">
+    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
         <v>0</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="25" customHeight="1">
-      <c r="A3" s="17">
+      <c r="C2" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
         <v>1</v>
       </c>
-      <c r="C3" s="21"/>
-    </row>
-    <row r="4" spans="1:3" ht="25" customHeight="1">
-      <c r="A4" s="17">
+      <c r="C3" s="22"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
         <v>1</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="25" customHeight="1">
-      <c r="A5" s="17">
+      <c r="C4" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
         <v>2</v>
       </c>
-      <c r="C5" s="21"/>
-    </row>
-    <row r="6" spans="1:3" ht="25" customHeight="1">
-      <c r="A6" s="17">
+      <c r="C5" s="22"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
         <v>2</v>
       </c>
-      <c r="C6" s="21"/>
-    </row>
-    <row r="7" spans="1:3" ht="25" customHeight="1">
-      <c r="A7" s="17">
+      <c r="C6" s="22"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
         <v>2</v>
       </c>
-      <c r="C7" s="21"/>
-    </row>
-    <row r="8" spans="1:3" ht="25" customHeight="1">
-      <c r="A8" s="17">
+      <c r="C7" s="22"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="25" customHeight="1">
-      <c r="A9" s="17">
+    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="25" customHeight="1">
-      <c r="A10" s="17">
+    <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="25" customHeight="1">
-      <c r="A11" s="17">
+    <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20">
         <v>5</v>
       </c>
     </row>
@@ -2107,74 +2221,74 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B80A013-0A29-48EB-BF14-19138E6CB3B9}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1">
-      <c r="A2" s="17">
+    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
         <v>5</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="25" customHeight="1">
-      <c r="A3" s="17">
+      <c r="C2" s="23" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
         <v>5.5</v>
       </c>
-      <c r="C3" s="21"/>
-    </row>
-    <row r="4" spans="1:3" ht="25" customHeight="1">
-      <c r="A4" s="17">
+      <c r="C3" s="22"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
         <v>6</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="25" customHeight="1">
-      <c r="A5" s="17">
+      <c r="C4" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
         <v>6</v>
       </c>
-      <c r="C5" s="21"/>
-    </row>
-    <row r="6" spans="1:3" ht="25" customHeight="1">
-      <c r="A6" s="17">
+      <c r="C5" s="22"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
         <v>6.5</v>
       </c>
-      <c r="C6" s="21"/>
-    </row>
-    <row r="7" spans="1:3" ht="25" customHeight="1">
-      <c r="A7" s="17">
+      <c r="C6" s="22"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
         <v>7</v>
       </c>
-      <c r="C7" s="21"/>
-    </row>
-    <row r="8" spans="1:3" ht="25" customHeight="1">
-      <c r="A8" s="17">
+      <c r="C7" s="22"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
         <v>7.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="25" customHeight="1">
-      <c r="A9" s="17">
+    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
         <v>8</v>
       </c>
     </row>
@@ -2183,164 +2297,164 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801E828C-B2D3-4518-A36E-3B611E5FAC89}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="22" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="1" max="2" width="22.625" customWidth="1"/>
+    <col min="4" max="4" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1" s="18" t="s">
+    <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
+        <v>2</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="23" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="25" customHeight="1">
-      <c r="A2" s="17">
-        <v>2</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="25" customHeight="1">
-      <c r="A3" s="17">
+    <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
         <v>3</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="D3" s="21"/>
-    </row>
-    <row r="4" spans="1:4" ht="25" customHeight="1">
-      <c r="A4" s="17">
+      <c r="B3" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="22"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
         <v>4</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="D5" s="21"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="D7" s="21"/>
+      <c r="B4" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" s="22"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="D4:D7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E644AB-0B1B-4C5F-B2FE-F08D1EBD0BD5}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="1" max="3" width="22.625" customWidth="1"/>
+    <col min="5" max="5" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="25" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="B2" s="17">
+    <row r="1" spans="1:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="20">
         <v>30</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="20">
         <v>40</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="25" customHeight="1">
-      <c r="A3" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="B3" s="17">
+      <c r="E2" s="23" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="20">
         <v>32</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="20">
         <v>80</v>
       </c>
-      <c r="E3" s="21"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="E4" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="E5" s="21"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="E6" s="21"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="E7" s="21"/>
+      <c r="E3" s="22"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6BB7994-4EE7-41C2-B17A-D91C7786BA34}">
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="17" width="13" customWidth="1"/>
+    <col min="1" max="1" width="13.625" customWidth="1"/>
+    <col min="2" max="2" width="23.625" customWidth="1"/>
+    <col min="3" max="17" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>50</v>
+    <row r="1" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2359,10 +2473,10 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:17" ht="22.1" customHeight="1">
+    <row r="2" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>51</v>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C2" s="1">
         <f>COUNT(Data!E2:E37)</f>
@@ -2383,7 +2497,7 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="22.1" customHeight="1">
+    <row r="3" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2402,30 +2516,30 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:17" ht="36" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>59</v>
+    <row r="4" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2437,34 +2551,34 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" ht="22.1" customHeight="1">
+    <row r="5" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="8">
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="10">
         <f>COUNTIFS(Data!$E$2:$E$37,A5)</f>
         <v>4</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="11">
         <f>C5/$C$2</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="12">
         <f>D5</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="10">
         <f>SUM($C$5:C5)</f>
         <v>4</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="11">
         <f>F5/$C$2</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="12">
         <f>G5</f>
         <v>0.1111111111111111</v>
       </c>
@@ -2478,35 +2592,35 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" ht="22.1" customHeight="1">
+    <row r="6" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="10">
         <f>COUNTIFS(Data!$E$2:$E$37,A6)</f>
         <v>10</v>
       </c>
-      <c r="D6" s="9">
-        <f>C6/$C$2</f>
+      <c r="D6" s="11">
+        <f t="shared" ref="D6:D8" si="0">C6/$C$2</f>
         <v>0.27777777777777779</v>
       </c>
-      <c r="E6" s="10">
-        <f>D6</f>
+      <c r="E6" s="12">
+        <f t="shared" ref="E6:E8" si="1">D6</f>
         <v>0.27777777777777779</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="10">
         <f>SUM($C$5:C6)</f>
         <v>14</v>
       </c>
-      <c r="G6" s="9">
-        <f>F6/$C$2</f>
+      <c r="G6" s="11">
+        <f t="shared" ref="G6:G8" si="2">F6/$C$2</f>
         <v>0.3888888888888889</v>
       </c>
-      <c r="H6" s="10">
-        <f>G6</f>
+      <c r="H6" s="12">
+        <f t="shared" ref="H6:H8" si="3">G6</f>
         <v>0.3888888888888889</v>
       </c>
       <c r="I6" s="1"/>
@@ -2519,35 +2633,35 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" ht="22.1" customHeight="1">
+    <row r="7" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="10">
         <f>COUNTIFS(Data!$E$2:$E$37,A7)</f>
         <v>14</v>
       </c>
-      <c r="D7" s="9">
-        <f>C7/$C$2</f>
+      <c r="D7" s="11">
+        <f t="shared" si="0"/>
         <v>0.3888888888888889</v>
       </c>
-      <c r="E7" s="10">
-        <f>D7</f>
+      <c r="E7" s="12">
+        <f t="shared" si="1"/>
         <v>0.3888888888888889</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="10">
         <f>SUM($C$5:C7)</f>
         <v>28</v>
       </c>
-      <c r="G7" s="9">
-        <f>F7/$C$2</f>
+      <c r="G7" s="11">
+        <f t="shared" si="2"/>
         <v>0.77777777777777779</v>
       </c>
-      <c r="H7" s="10">
-        <f>G7</f>
+      <c r="H7" s="12">
+        <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="I7" s="1"/>
@@ -2560,35 +2674,35 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" ht="22.1" customHeight="1">
+    <row r="8" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10">
         <f>COUNTIFS(Data!$E$2:$E$37,A8)</f>
         <v>8</v>
       </c>
-      <c r="D8" s="9">
-        <f>C8/$C$2</f>
+      <c r="D8" s="11">
+        <f t="shared" si="0"/>
         <v>0.22222222222222221</v>
       </c>
-      <c r="E8" s="10">
-        <f>D8</f>
+      <c r="E8" s="12">
+        <f t="shared" si="1"/>
         <v>0.22222222222222221</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="10">
         <f>SUM($C$5:C8)</f>
         <v>36</v>
       </c>
-      <c r="G8" s="9">
-        <f>F8/$C$2</f>
+      <c r="G8" s="11">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H8" s="10">
-        <f>G8</f>
+      <c r="H8" s="12">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I8" s="1"/>
@@ -2601,12 +2715,12 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" ht="22.1" customHeight="1">
+    <row r="9" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -2620,20 +2734,20 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" ht="22.1" customHeight="1">
+    <row r="10" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="13">
         <f>SUM(C5:C8)</f>
         <v>36</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="14">
         <f>SUM(D5:D8)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="15">
         <f>D10</f>
         <v>1</v>
       </c>
@@ -2650,7 +2764,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" ht="22.1" customHeight="1">
+    <row r="11" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2669,9 +2783,9 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A12" s="14" t="s">
-        <v>65</v>
+    <row r="12" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2690,9 +2804,9 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A13" s="14" t="s">
-        <v>66</v>
+    <row r="13" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -2711,7 +2825,7 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="22.1" customHeight="1">
+    <row r="14" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -2730,9 +2844,9 @@
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>67</v>
+    <row r="15" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2751,7 +2865,7 @@
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" ht="22.1" customHeight="1">
+    <row r="16" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -2770,7 +2884,7 @@
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:17" ht="22.1" customHeight="1">
+    <row r="17" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2789,7 +2903,7 @@
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:17" ht="22.1" customHeight="1">
+    <row r="18" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2808,7 +2922,7 @@
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="1:17" ht="22.1" customHeight="1">
+    <row r="19" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2827,7 +2941,7 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:17" ht="22.1" customHeight="1">
+    <row r="20" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2846,7 +2960,7 @@
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:17" ht="22.1" customHeight="1">
+    <row r="21" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2865,7 +2979,7 @@
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:17" ht="22.1" customHeight="1">
+    <row r="22" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2884,7 +2998,7 @@
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:17" ht="22.1" customHeight="1">
+    <row r="23" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2903,7 +3017,7 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:17" ht="22.1" customHeight="1">
+    <row r="24" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2922,7 +3036,7 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:17" ht="22.1" customHeight="1">
+    <row r="25" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2941,7 +3055,7 @@
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" spans="1:17" ht="22.1" customHeight="1">
+    <row r="26" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2960,7 +3074,7 @@
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" spans="1:17" ht="22.1" customHeight="1">
+    <row r="27" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2979,7 +3093,7 @@
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" spans="1:17" ht="22.1" customHeight="1">
+    <row r="28" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2998,7 +3112,7 @@
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:17" ht="22.1" customHeight="1">
+    <row r="29" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -3017,7 +3131,7 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:17" ht="22.1" customHeight="1">
+    <row r="30" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -3036,7 +3150,7 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" spans="1:17" ht="22.1" customHeight="1">
+    <row r="31" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -3055,7 +3169,7 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="1:17" ht="22.1" customHeight="1">
+    <row r="32" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -3074,7 +3188,7 @@
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="1:17" ht="22.1" customHeight="1">
+    <row r="33" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -3093,7 +3207,7 @@
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" spans="1:17" ht="22.1" customHeight="1">
+    <row r="34" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3112,7 +3226,7 @@
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35" spans="1:17" ht="22.1" customHeight="1">
+    <row r="35" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -3131,7 +3245,7 @@
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36" spans="1:17" ht="22.1" customHeight="1">
+    <row r="36" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -3150,7 +3264,7 @@
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37" spans="1:17" ht="22.1" customHeight="1">
+    <row r="37" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -3169,7 +3283,7 @@
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38" spans="1:17" ht="22.1" customHeight="1">
+    <row r="38" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -3188,7 +3302,7 @@
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" spans="1:17" ht="22.1" customHeight="1">
+    <row r="39" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -3207,7 +3321,7 @@
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
     </row>
-    <row r="40" spans="1:17" ht="22.1" customHeight="1">
+    <row r="40" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -3227,25 +3341,25 @@
       <c r="Q40" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE3BA28-C601-4825-97E2-30D5042265B8}">
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="17" width="13" customWidth="1"/>
+    <col min="1" max="1" width="13.625" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="4" max="17" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>68</v>
+    <row r="1" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3264,10 +3378,10 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:17" ht="22.1" customHeight="1">
+    <row r="2" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>69</v>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="C2" s="1">
         <f>COUNT(Data!B2:B37)</f>
@@ -3288,7 +3402,7 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="22.1" customHeight="1">
+    <row r="3" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -3307,24 +3421,24 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:17" ht="36" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>56</v>
+    <row r="4" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -3338,26 +3452,26 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" ht="22.1" customHeight="1">
+    <row r="5" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="10">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A5,Data!$B$2:$B$37,"&lt;="&amp;B5)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="9">
-        <f t="shared" ref="E5:E10" si="0">D5/$C$2</f>
+      <c r="E5" s="11">
+        <f>D5/$C$2</f>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="F5" s="10">
-        <f t="shared" ref="F5:F10" si="1">E5</f>
+      <c r="F5" s="12">
+        <f>E5</f>
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="G5" s="1"/>
@@ -3372,26 +3486,26 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" ht="22.1" customHeight="1">
+    <row r="6" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="8">
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="10">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A6,Data!$B$2:$B$37,"&lt;="&amp;B6)</f>
         <v>5</v>
       </c>
-      <c r="E6" s="9">
-        <f t="shared" si="0"/>
+      <c r="E6" s="11">
+        <f t="shared" ref="E6:E10" si="0">D6/$C$2</f>
         <v>0.15151515151515152</v>
       </c>
-      <c r="F6" s="10">
-        <f t="shared" si="1"/>
+      <c r="F6" s="12">
+        <f t="shared" ref="F6:F10" si="1">E6</f>
         <v>0.15151515151515152</v>
       </c>
       <c r="G6" s="1"/>
@@ -3406,25 +3520,25 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" ht="22.1" customHeight="1">
+    <row r="7" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>7</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="10">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A7,Data!$B$2:$B$37,"&lt;="&amp;B7)</f>
         <v>8</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="11">
         <f t="shared" si="0"/>
         <v>0.24242424242424243</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="12">
         <f t="shared" si="1"/>
         <v>0.24242424242424243</v>
       </c>
@@ -3440,25 +3554,25 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" ht="22.1" customHeight="1">
+    <row r="8" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="8">
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="10">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A8,Data!$B$2:$B$37,"&lt;="&amp;B8)</f>
         <v>10</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="11">
         <f t="shared" si="0"/>
         <v>0.30303030303030304</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="12">
         <f t="shared" si="1"/>
         <v>0.30303030303030304</v>
       </c>
@@ -3474,25 +3588,25 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" ht="22.1" customHeight="1">
+    <row r="9" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="8">
+      <c r="C9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="10">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A9,Data!$B$2:$B$37,"&lt;="&amp;B9)</f>
         <v>5</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="11">
         <f t="shared" si="0"/>
         <v>0.15151515151515152</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="12">
         <f t="shared" si="1"/>
         <v>0.15151515151515152</v>
       </c>
@@ -3508,25 +3622,25 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" ht="22.1" customHeight="1">
+    <row r="10" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1">
         <v>10</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="8">
+      <c r="C10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="10">
         <f>COUNTIFS(Data!$B$2:$B$37,"&gt;"&amp;A10,Data!$B$2:$B$37,"&lt;="&amp;B10)</f>
         <v>2</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="11">
         <f t="shared" si="0"/>
         <v>6.0606060606060608E-2</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="12">
         <f t="shared" si="1"/>
         <v>6.0606060606060608E-2</v>
       </c>
@@ -3542,13 +3656,13 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" ht="22.1" customHeight="1">
+    <row r="11" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="7"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -3561,21 +3675,21 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="22.1" customHeight="1">
+    <row r="12" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="11">
+      <c r="C12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="13">
         <f>SUM(D5:D10)</f>
         <v>33</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="14">
         <f>SUM(E5:E10)</f>
         <v>1</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="15">
         <f>E12</f>
         <v>1</v>
       </c>
@@ -3591,7 +3705,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" ht="22.1" customHeight="1">
+    <row r="13" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -3610,9 +3724,9 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A14" s="14" t="s">
-        <v>79</v>
+    <row r="14" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>29</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -3631,9 +3745,9 @@
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>80</v>
+    <row r="15" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -3652,7 +3766,7 @@
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" ht="22.1" customHeight="1">
+    <row r="16" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -3671,9 +3785,9 @@
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>81</v>
+    <row r="17" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -3692,9 +3806,9 @@
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A18" s="14" t="s">
-        <v>82</v>
+    <row r="18" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -3713,7 +3827,7 @@
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="1:17" ht="22.1" customHeight="1">
+    <row r="19" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -3732,7 +3846,7 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:17" ht="22.1" customHeight="1">
+    <row r="20" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -3751,7 +3865,7 @@
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:17" ht="22.1" customHeight="1">
+    <row r="21" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -3770,7 +3884,7 @@
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:17" ht="22.1" customHeight="1">
+    <row r="22" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -3789,7 +3903,7 @@
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:17" ht="22.1" customHeight="1">
+    <row r="23" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -3808,7 +3922,7 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:17" ht="22.1" customHeight="1">
+    <row r="24" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -3827,7 +3941,7 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:17" ht="22.1" customHeight="1">
+    <row r="25" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -3846,7 +3960,7 @@
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" spans="1:17" ht="22.1" customHeight="1">
+    <row r="26" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -3865,7 +3979,7 @@
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" spans="1:17" ht="22.1" customHeight="1">
+    <row r="27" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -3884,7 +3998,7 @@
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" spans="1:17" ht="22.1" customHeight="1">
+    <row r="28" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -3903,7 +4017,7 @@
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:17" ht="22.1" customHeight="1">
+    <row r="29" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -3922,7 +4036,7 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:17" ht="22.1" customHeight="1">
+    <row r="30" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -3941,7 +4055,7 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" spans="1:17" ht="22.1" customHeight="1">
+    <row r="31" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -3960,7 +4074,7 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="1:17" ht="22.1" customHeight="1">
+    <row r="32" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -3979,7 +4093,7 @@
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="1:17" ht="22.1" customHeight="1">
+    <row r="33" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -3998,7 +4112,7 @@
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" spans="1:17" ht="22.1" customHeight="1">
+    <row r="34" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -4017,7 +4131,7 @@
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35" spans="1:17" ht="22.1" customHeight="1">
+    <row r="35" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -4036,7 +4150,7 @@
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36" spans="1:17" ht="22.1" customHeight="1">
+    <row r="36" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -4055,7 +4169,7 @@
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37" spans="1:17" ht="22.1" customHeight="1">
+    <row r="37" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -4074,7 +4188,7 @@
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38" spans="1:17" ht="22.1" customHeight="1">
+    <row r="38" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -4093,7 +4207,7 @@
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" spans="1:17" ht="22.1" customHeight="1">
+    <row r="39" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -4112,7 +4226,7 @@
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
     </row>
-    <row r="40" spans="1:17" ht="22.1" customHeight="1">
+    <row r="40" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -4132,40 +4246,40 @@
       <c r="Q40" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC557E6-E98C-4B6E-AB7F-9141D04A6B10}">
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="17" width="13" customWidth="1"/>
+    <col min="1" max="3" width="13.625" customWidth="1"/>
+    <col min="4" max="4" width="19.625" customWidth="1"/>
+    <col min="5" max="17" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="36" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>87</v>
+    <row r="1" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
-        <v>88</v>
+      <c r="G1" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -4178,20 +4292,20 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="15">
+    <row r="2" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="17">
         <v>6</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="18">
         <v>5</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="16">
+      <c r="D2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="18">
         <v>2</v>
       </c>
       <c r="F2" s="1"/>
@@ -4207,25 +4321,25 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="15">
+    <row r="3" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="17">
         <v>8</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="18">
         <v>9</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="16">
+      <c r="D3" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="18">
         <v>4</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="14" t="s">
-        <v>93</v>
+      <c r="G3" s="16" t="s">
+        <v>77</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -4238,25 +4352,25 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="15">
+    <row r="4" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="17">
         <v>7</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="18">
         <v>8</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="16">
+      <c r="D4" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="18">
         <v>3</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="14" t="s">
-        <v>95</v>
+      <c r="G4" s="16" t="s">
+        <v>78</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -4269,25 +4383,25 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="15">
+    <row r="5" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="17">
         <v>5</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="18">
         <v>6</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="16">
+      <c r="D5" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="18">
         <v>2</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="14" t="s">
-        <v>97</v>
+      <c r="G5" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -4300,23 +4414,23 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16">
+    <row r="6" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18">
         <v>7</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="16">
+      <c r="D6" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="18">
         <v>3</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="14" t="s">
-        <v>99</v>
+      <c r="G6" s="16" t="s">
+        <v>80</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -4329,25 +4443,25 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="15">
+    <row r="7" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="17">
         <v>7</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="18">
         <v>0</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="16">
+      <c r="D7" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="18">
         <v>1</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="14" t="s">
-        <v>101</v>
+      <c r="G7" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -4360,25 +4474,25 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="15">
+    <row r="8" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="17">
         <v>4.5</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="18">
         <v>2</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" s="16">
+      <c r="D8" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="18">
         <v>1</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="14" t="s">
-        <v>103</v>
+      <c r="G8" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -4391,25 +4505,25 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B9" s="15">
+    <row r="9" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="17">
         <v>6.3</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="18">
         <v>7</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" s="16">
+      <c r="D9" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="18">
         <v>3</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="14" t="s">
-        <v>105</v>
+      <c r="G9" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -4422,25 +4536,25 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="15">
+    <row r="10" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="17">
         <v>7.3</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="18">
         <v>9</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="D10" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="18">
         <v>4</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="14" t="s">
-        <v>107</v>
+      <c r="G10" s="16" t="s">
+        <v>84</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -4453,25 +4567,25 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B11" s="15">
+    <row r="11" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="17">
         <v>8.1</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="18">
         <v>4</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="16">
+      <c r="D11" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="18">
         <v>2</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="14" t="s">
-        <v>109</v>
+      <c r="G11" s="16" t="s">
+        <v>85</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -4484,23 +4598,23 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16">
+    <row r="12" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18">
         <v>7</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="16">
+      <c r="D12" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="18">
         <v>3</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="14" t="s">
-        <v>111</v>
+      <c r="G12" s="16" t="s">
+        <v>86</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -4513,20 +4627,20 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" s="15">
+    <row r="13" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="17">
         <v>6</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="18">
         <v>10</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="16">
+      <c r="D13" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="18">
         <v>2</v>
       </c>
       <c r="F13" s="1"/>
@@ -4542,20 +4656,20 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="15">
+    <row r="14" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="17">
         <v>7.1</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="18">
         <v>5</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="16">
+      <c r="D14" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="18">
         <v>3</v>
       </c>
       <c r="F14" s="1"/>
@@ -4571,20 +4685,20 @@
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="15">
+    <row r="15" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="17">
         <v>7.9</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="18">
         <v>8</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="16">
+      <c r="D15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="18">
         <v>1</v>
       </c>
       <c r="F15" s="1"/>
@@ -4600,20 +4714,20 @@
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" s="15">
+    <row r="16" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="17">
         <v>9.1999999999999993</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="18">
         <v>11</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="16">
+      <c r="D16" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="18">
         <v>3</v>
       </c>
       <c r="F16" s="1"/>
@@ -4629,20 +4743,20 @@
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17" s="15">
+    <row r="17" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="17">
         <v>5.5</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="18">
         <v>6</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="16">
+      <c r="D17" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="18">
         <v>4</v>
       </c>
       <c r="F17" s="1"/>
@@ -4658,20 +4772,20 @@
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A18" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="15">
+    <row r="18" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="17">
         <v>6.8</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="18">
         <v>8</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="16">
+      <c r="D18" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="18">
         <v>2</v>
       </c>
       <c r="F18" s="1"/>
@@ -4687,20 +4801,20 @@
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A19" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="15">
+    <row r="19" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="17">
         <v>7.5</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="18">
         <v>3</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="16">
+      <c r="D19" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="18">
         <v>4</v>
       </c>
       <c r="F19" s="1"/>
@@ -4716,20 +4830,20 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A20" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B20" s="15">
+    <row r="20" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="17">
         <v>8.8000000000000007</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="18">
         <v>7</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E20" s="16">
+      <c r="D20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="18">
         <v>2</v>
       </c>
       <c r="F20" s="1"/>
@@ -4745,20 +4859,20 @@
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A21" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B21" s="15">
+    <row r="21" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="17">
         <v>4.8</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="18">
         <v>9</v>
       </c>
-      <c r="D21" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="16">
+      <c r="D21" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="18">
         <v>3</v>
       </c>
       <c r="F21" s="1"/>
@@ -4774,20 +4888,20 @@
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="15">
+    <row r="22" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="17">
         <v>6.5</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="18">
         <v>5</v>
       </c>
-      <c r="D22" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="16">
+      <c r="D22" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="18">
         <v>1</v>
       </c>
       <c r="F22" s="1"/>
@@ -4803,20 +4917,20 @@
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="15">
+    <row r="23" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="17">
         <v>7.4</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="18">
         <v>7</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="16">
+      <c r="D23" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="18">
         <v>3</v>
       </c>
       <c r="F23" s="1"/>
@@ -4832,20 +4946,20 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="15">
+    <row r="24" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="17">
         <v>8.3000000000000007</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="18">
         <v>10</v>
       </c>
-      <c r="D24" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="16">
+      <c r="D24" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="18">
         <v>4</v>
       </c>
       <c r="F24" s="1"/>
@@ -4861,18 +4975,18 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A25" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="16">
+    <row r="25" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="18">
         <v>6</v>
       </c>
-      <c r="D25" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" s="16">
+      <c r="D25" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="18">
         <v>3</v>
       </c>
       <c r="F25" s="1"/>
@@ -4888,20 +5002,20 @@
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B26" s="15">
+    <row r="26" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="17">
         <v>6.2</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="18">
         <v>8</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="16">
+      <c r="D26" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="18">
         <v>4</v>
       </c>
       <c r="F26" s="1"/>
@@ -4917,20 +5031,20 @@
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A27" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" s="15">
+    <row r="27" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="17">
         <v>7.2</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="18">
         <v>12</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" s="16">
+      <c r="D27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="18">
         <v>2</v>
       </c>
       <c r="F27" s="1"/>
@@ -4946,20 +5060,20 @@
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A28" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B28" s="15">
+    <row r="28" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="17">
         <v>8</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="18">
         <v>6</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="16">
+      <c r="D28" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="18">
         <v>3</v>
       </c>
       <c r="F28" s="1"/>
@@ -4975,20 +5089,20 @@
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="15">
+    <row r="29" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="17">
         <v>9.5</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="18">
         <v>9</v>
       </c>
-      <c r="D29" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="16">
+      <c r="D29" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="18">
         <v>2</v>
       </c>
       <c r="F29" s="1"/>
@@ -5004,20 +5118,20 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B30" s="15">
+    <row r="30" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="17">
         <v>5.8</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="18">
         <v>4</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="16">
+      <c r="D30" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="18">
         <v>3</v>
       </c>
       <c r="F30" s="1"/>
@@ -5033,20 +5147,20 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B31" s="15">
+    <row r="31" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="17">
         <v>7</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="18">
         <v>7</v>
       </c>
-      <c r="D31" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" s="16">
+      <c r="D31" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="18">
         <v>4</v>
       </c>
       <c r="F31" s="1"/>
@@ -5062,20 +5176,20 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B32" s="15">
+    <row r="32" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="17">
         <v>7.7</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="18">
         <v>10</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" s="16">
+      <c r="D32" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="18">
         <v>3</v>
       </c>
       <c r="F32" s="1"/>
@@ -5091,20 +5205,20 @@
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B33" s="15">
+    <row r="33" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="17">
         <v>9</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="18">
         <v>5</v>
       </c>
-      <c r="D33" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="16">
+      <c r="D33" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="18">
         <v>4</v>
       </c>
       <c r="F33" s="1"/>
@@ -5120,20 +5234,20 @@
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B34" s="15">
+    <row r="34" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="17">
         <v>5.2</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="18">
         <v>8</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E34" s="16">
+      <c r="D34" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="18">
         <v>2</v>
       </c>
       <c r="F34" s="1"/>
@@ -5149,20 +5263,20 @@
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B35" s="15">
+    <row r="35" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="17">
         <v>6.5</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="18">
         <v>11</v>
       </c>
-      <c r="D35" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E35" s="16">
+      <c r="D35" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="18">
         <v>3</v>
       </c>
       <c r="F35" s="1"/>
@@ -5178,20 +5292,20 @@
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B36" s="15">
+    <row r="36" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="17">
         <v>7.5</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="18">
         <v>6</v>
       </c>
-      <c r="D36" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E36" s="16">
+      <c r="D36" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="18">
         <v>2</v>
       </c>
       <c r="F36" s="1"/>
@@ -5207,20 +5321,20 @@
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37" spans="1:17" ht="22.1" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B37" s="15">
+    <row r="37" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="17">
         <v>8.5</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="18">
         <v>8</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E37" s="16">
+      <c r="D37" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="18">
         <v>3</v>
       </c>
       <c r="F37" s="1"/>
@@ -5236,7 +5350,7 @@
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38" spans="1:17" ht="22.1" customHeight="1">
+    <row r="38" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -5255,7 +5369,7 @@
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" spans="1:17" ht="22.1" customHeight="1">
+    <row r="39" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -5274,7 +5388,7 @@
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
     </row>
-    <row r="40" spans="1:17" ht="22.1" customHeight="1">
+    <row r="40" spans="1:17" ht="22.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -5295,485 +5409,485 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="whole" sqref="E2:E37" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="whole" showInputMessage="1" sqref="E2:E37" xr:uid="{81609B10-FAA2-4A25-9464-7A59C2DE3AC6}">
       <formula1>1</formula1>
       <formula2>4</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="C2:C37" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="whole" showInputMessage="1" sqref="C2:C37" xr:uid="{AC56D774-C098-4D6F-84B2-88FD91A2A829}">
       <formula1>0</formula1>
       <formula2>12</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A703E3B-F619-4A80-9081-6FFD1CA2DBF2}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="22" customWidth="1"/>
-    <col min="7" max="7" width="60" customWidth="1"/>
+    <col min="1" max="5" width="22.625" customWidth="1"/>
+    <col min="7" max="7" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="4" t="s">
+    <row r="1" spans="1:7" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="25" customHeight="1">
-      <c r="A2" s="17" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="20">
+        <v>6</v>
+      </c>
+      <c r="C2" s="20">
+        <v>5</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="20">
+        <v>2</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="20">
+        <v>8</v>
+      </c>
+      <c r="C3" s="20">
+        <v>9</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="20">
+        <v>4</v>
+      </c>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="20">
+        <v>7</v>
+      </c>
+      <c r="C4" s="20">
+        <v>8</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="20">
+        <v>3</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="17">
+    </row>
+    <row r="5" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="20">
+        <v>5</v>
+      </c>
+      <c r="C5" s="20">
         <v>6</v>
       </c>
-      <c r="C2" s="17">
-        <v>5</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="17">
+      <c r="D5" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="20">
         <v>2</v>
       </c>
-      <c r="G2" s="21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="25" customHeight="1">
-      <c r="A3" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="17">
-        <v>8</v>
-      </c>
-      <c r="C3" s="17">
-        <v>9</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="17">
-        <v>4</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" spans="1:7" ht="25" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="17">
+      <c r="G5" s="22"/>
+    </row>
+    <row r="6" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20">
         <v>7</v>
       </c>
-      <c r="C4" s="17">
-        <v>8</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="17">
+      <c r="D6" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="20">
         <v>3</v>
       </c>
-      <c r="G4" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="25" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="17">
-        <v>5</v>
-      </c>
-      <c r="C5" s="17">
-        <v>6</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="17">
-        <v>2</v>
-      </c>
-      <c r="G5" s="21"/>
-    </row>
-    <row r="6" spans="1:7" ht="25" customHeight="1">
-      <c r="A6" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17">
+      <c r="G6" s="22"/>
+    </row>
+    <row r="7" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="20">
         <v>7</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="17">
-        <v>3</v>
-      </c>
-      <c r="G6" s="21"/>
-    </row>
-    <row r="7" spans="1:7" ht="25" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="17">
-        <v>7</v>
-      </c>
-      <c r="C7" s="17">
+      <c r="C7" s="20">
         <v>0</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="17">
+      <c r="D7" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="20">
         <v>1</v>
       </c>
-      <c r="G7" s="21"/>
+      <c r="G7" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88BDAED-8E87-4EE2-B10E-84FA288C7BD0}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="22" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="1" max="2" width="22.625" customWidth="1"/>
+    <col min="4" max="4" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="25" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="17">
+    <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="20">
         <v>14</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="25" customHeight="1">
-      <c r="A3" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="17">
+      <c r="D2" s="23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="20">
         <v>12</v>
       </c>
-      <c r="D3" s="21"/>
-    </row>
-    <row r="4" spans="1:4" ht="25" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="17">
+      <c r="D3" s="22"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="20">
         <v>10</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="D5" s="21"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="D7" s="21"/>
+      <c r="D4" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" s="22"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="D4:D7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83B97B4E-AEE7-4C5B-A012-4F1FD75151F2}">
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="22" customWidth="1"/>
-    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="1" max="7" width="22.625" customWidth="1"/>
+    <col min="9" max="9" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="25" customHeight="1">
-      <c r="A2" s="17">
+    <row r="1" spans="1:9" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
         <v>1</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="20">
         <v>1</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="20">
         <v>1</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="20">
         <v>1</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="20">
         <v>1</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F2" s="20">
         <v>4</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="20">
         <v>1</v>
       </c>
-      <c r="I2" s="21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="25" customHeight="1">
-      <c r="A3" s="17">
+      <c r="I2" s="23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
         <v>2</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="20">
         <v>2</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="20">
         <v>3</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="20">
         <v>1</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="20">
         <v>6</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="20">
         <v>4</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="20">
         <v>3</v>
       </c>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="1:9" ht="25" customHeight="1">
-      <c r="A4" s="17">
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
         <v>3</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="20">
         <v>4</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="20">
         <v>10</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="20">
         <v>2</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="20">
         <v>10</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="20">
         <v>4</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="20">
         <v>8</v>
       </c>
-      <c r="I4" s="21" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="25" customHeight="1">
-      <c r="A5" s="17">
+      <c r="I4" s="23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="20">
         <v>7</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="20">
         <v>8</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="20">
         <v>3</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="20">
         <v>4</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="20">
         <v>4</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="20">
         <v>9</v>
       </c>
-      <c r="I5" s="21"/>
-    </row>
-    <row r="6" spans="1:9" ht="25" customHeight="1">
-      <c r="A6" s="17">
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
         <v>5</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="20">
         <v>10</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="20">
         <v>5</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="20">
         <v>5</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="20">
         <v>1</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="20">
         <v>4</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="20">
         <v>4</v>
       </c>
-      <c r="I6" s="21"/>
-    </row>
-    <row r="7" spans="1:9" ht="25" customHeight="1">
-      <c r="A7" s="17">
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
         <v>6</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="20">
         <v>7</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="20">
         <v>3</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="20">
         <v>8</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="20">
         <v>4</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="20">
         <v>4</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="20">
         <v>1</v>
       </c>
-      <c r="I7" s="21"/>
-    </row>
-    <row r="8" spans="1:9" ht="25" customHeight="1">
-      <c r="A8" s="17">
+      <c r="I7" s="22"/>
+    </row>
+    <row r="8" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
         <v>7</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="20">
         <v>4</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="20">
         <v>2</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="20">
         <v>10</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="20">
         <v>10</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="20">
         <v>4</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="25" customHeight="1">
-      <c r="A9" s="17">
+    <row r="9" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
         <v>8</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="20">
         <v>2</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="20">
         <v>1</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="20">
         <v>3</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="20">
         <v>6</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="25" customHeight="1">
-      <c r="A10" s="17">
+    <row r="10" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
         <v>9</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="20">
         <v>1</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="20">
         <v>1</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="20">
         <v>1</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="20">
         <v>1</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="20">
         <v>4</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="20">
         <v>1</v>
       </c>
     </row>
@@ -5782,183 +5896,183 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I4:I7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C61B1747-BEB9-40A8-8777-F310E037F114}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="1" max="3" width="22.625" customWidth="1"/>
+    <col min="5" max="5" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="25" customHeight="1">
-      <c r="A2" s="17">
+    <row r="1" spans="1:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
         <v>0</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="20">
         <v>15</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="20">
         <v>0</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="25" customHeight="1">
-      <c r="A3" s="17">
+      <c r="E2" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
         <v>1</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="20">
         <v>7</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="20">
         <v>0</v>
       </c>
-      <c r="E3" s="21"/>
-    </row>
-    <row r="4" spans="1:5" ht="25" customHeight="1">
-      <c r="A4" s="17">
+      <c r="E3" s="22"/>
+    </row>
+    <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
         <v>2</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="20">
         <v>4</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="20">
         <v>0</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="25" customHeight="1">
-      <c r="A5" s="17">
+      <c r="E4" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
         <v>3</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="20">
         <v>3</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="20">
         <v>1</v>
       </c>
-      <c r="E5" s="21"/>
-    </row>
-    <row r="6" spans="1:5" ht="25" customHeight="1">
-      <c r="A6" s="17">
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
         <v>4</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="20">
         <v>2</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="20">
         <v>1</v>
       </c>
-      <c r="E6" s="21"/>
-    </row>
-    <row r="7" spans="1:5" ht="25" customHeight="1">
-      <c r="A7" s="17">
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
         <v>5</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="20">
         <v>1</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="20">
         <v>1</v>
       </c>
-      <c r="E7" s="21"/>
-    </row>
-    <row r="8" spans="1:5" ht="25" customHeight="1">
-      <c r="A8" s="17">
+      <c r="E7" s="22"/>
+    </row>
+    <row r="8" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
         <v>6</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="20">
         <v>1</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="25" customHeight="1">
-      <c r="A9" s="17">
+    <row r="9" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
         <v>7</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="20">
         <v>1</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="25" customHeight="1">
-      <c r="A10" s="17">
+    <row r="10" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
         <v>8</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="20">
         <v>1</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="20">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="25" customHeight="1">
-      <c r="A11" s="17">
+    <row r="11" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20">
         <v>9</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="20">
         <v>1</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="25" customHeight="1">
-      <c r="A12" s="17">
+    <row r="12" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
         <v>10</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="20">
         <v>0</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="20">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="25" customHeight="1">
-      <c r="A13" s="17">
+    <row r="13" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
         <v>11</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="20">
         <v>0</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="20">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="25" customHeight="1">
-      <c r="A14" s="17">
+    <row r="14" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="20">
         <v>12</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="20">
         <v>0</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="20">
         <v>15</v>
       </c>
     </row>
@@ -5967,74 +6081,74 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{605B8CF8-E25A-4F49-A6D0-AE007701391D}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="13.6"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="46.05" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1">
-      <c r="A2" s="17">
+    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
         <v>12</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="25" customHeight="1">
-      <c r="A3" s="17">
+      <c r="C2" s="23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
         <v>14</v>
       </c>
-      <c r="C3" s="21"/>
-    </row>
-    <row r="4" spans="1:3" ht="25" customHeight="1">
-      <c r="A4" s="17">
+      <c r="C3" s="22"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
         <v>14</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="25" customHeight="1">
-      <c r="A5" s="17">
+      <c r="C4" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
         <v>18</v>
       </c>
-      <c r="C5" s="21"/>
-    </row>
-    <row r="6" spans="1:3" ht="25" customHeight="1">
-      <c r="A6" s="17">
+      <c r="C5" s="22"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
         <v>21</v>
       </c>
-      <c r="C6" s="21"/>
-    </row>
-    <row r="7" spans="1:3" ht="25" customHeight="1">
-      <c r="A7" s="17">
+      <c r="C6" s="22"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
         <v>23</v>
       </c>
-      <c r="C7" s="21"/>
-    </row>
-    <row r="8" spans="1:3" ht="25" customHeight="1">
-      <c r="A8" s="17">
+      <c r="C7" s="22"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="25" customHeight="1">
-      <c r="A9" s="17">
+    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
         <v>31</v>
       </c>
     </row>
@@ -6043,6 +6157,6 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>